--- a/data/BayesTrip_Data.xlsx
+++ b/data/BayesTrip_Data.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="01_Place_Master" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="07_Coordinates" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -986,4 +987,505 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>place_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>lat</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>lng</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Marina Beach</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>13.0532752</v>
+      </c>
+      <c r="D2" t="n">
+        <v>80.28331059999999</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>OSM Nominatim</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Fort St. George</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>13.0798617</v>
+      </c>
+      <c r="D3" t="n">
+        <v>80.2846692</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>OSM Nominatim</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>P03</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kapaleeshwarar Temple</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>13.0334336</v>
+      </c>
+      <c r="D4" t="n">
+        <v>80.26869600000001</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>OSM Nominatim</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>P04</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>San Thome Basilica</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>13.0335889</v>
+      </c>
+      <c r="D5" t="n">
+        <v>80.2777851</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>OSM Nominatim</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Government Museum, Chennai</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>13.0712808</v>
+      </c>
+      <c r="D6" t="n">
+        <v>80.25704330000001</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>OSM Nominatim</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>P06</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Guindy National Park</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>13.000005</v>
+      </c>
+      <c r="D7" t="n">
+        <v>80.22804480000001</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>OSM Nominatim</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>P07</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Arignar Anna Zoological Park (Vandalur Zoo)</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>12.8800708</v>
+      </c>
+      <c r="D8" t="n">
+        <v>80.08234539999999</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>OSM Nominatim</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>P08</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Valluvar Kottam</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>13.0540763</v>
+      </c>
+      <c r="D9" t="n">
+        <v>80.2418275</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>OSM Nominatim</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>P09</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Birla Planetarium</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>13.0119591</v>
+      </c>
+      <c r="D10" t="n">
+        <v>80.2440161</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>OSM Nominatim</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Semmozhi Poonga</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>13.0506767</v>
+      </c>
+      <c r="D11" t="n">
+        <v>80.2514735</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>OSM Nominatim</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Elliot's Beach</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>12.9969493</v>
+      </c>
+      <c r="D12" t="n">
+        <v>80.27087059999999</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>OSM Nominatim</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>P12</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Besant Nagar Beach</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>12.9978811</v>
+      </c>
+      <c r="D13" t="n">
+        <v>80.2718515</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>OSM Nominatim</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>P13</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>DakshinaChitra</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>12.822513</v>
+      </c>
+      <c r="D14" t="n">
+        <v>80.2435254</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>OSM Overpass (name-substring search; not indexed by Nominatim)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>P14</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Cholamandal Artists' Village</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>12.9224139</v>
+      </c>
+      <c r="D15" t="n">
+        <v>80.2522779</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>OSM Nominatim</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>P15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Vivekananda House</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>13.0495712</v>
+      </c>
+      <c r="D16" t="n">
+        <v>80.2802712</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>OSM Nominatim</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>P16</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Thousand Lights Mosque</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>13.0550988</v>
+      </c>
+      <c r="D17" t="n">
+        <v>80.255239</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>OSM Nominatim</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>P17</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Parthasarathy Temple</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>13.0538288</v>
+      </c>
+      <c r="D18" t="n">
+        <v>80.2778941</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>OSM Nominatim</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>P18</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Vadapalani Murugan Temple</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>13.0529847</v>
+      </c>
+      <c r="D19" t="n">
+        <v>80.21426409999999</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>OSM Nominatim</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>P19</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Express Avenue</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>13.0588206</v>
+      </c>
+      <c r="D20" t="n">
+        <v>80.2641028</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>OSM Nominatim</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>P20</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>MGM Dizzee World</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>12.8258571</v>
+      </c>
+      <c r="D21" t="n">
+        <v>80.2452821</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>OSM Nominatim</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/BayesTrip_Data.xlsx
+++ b/data/BayesTrip_Data.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="01_Place_Master" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="07_Coordinates" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="04_HMM_Initial" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1488,4 +1489,465 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>place_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>travel_time_seconds</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>raw_score</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>pi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Marina Beach</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>313.5</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.003189792663476874</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.07560111097594464</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Fort St. George</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>162.7</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.006146281499692687</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.1456727000058921</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>P03</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kapaleeshwarar Temple</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>536.3</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.001864628006712661</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.04419345196897007</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>P04</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>San Thome Basilica</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>451.4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.002215330084182543</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.05250542377261553</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Government Museum, Chennai</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>291</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.003436426116838488</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.08144655770088882</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>P06</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Guindy National Park</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1129.9</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.0008850340738118417</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.02097614681915094</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>P07</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Arignar Anna Zoological Park (Vandalur Zoo)</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>2185.4</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.0004575821359934108</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.01084513054404624</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>P08</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Valluvar Kottam</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>463.2</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.002158894645941278</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.0511678503690817</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>P09</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Birla Planetarium</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>924.1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.001082133968185261</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.02564760122384876</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Semmozhi Poonga</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>398.8</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.002507522567703109</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.05943066271554324</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Elliot's Beach</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>942.3</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.001061233152923697</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.02515223208209556</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>P12</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Besant Nagar Beach</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>951.4</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.001051082615093546</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.02491165470985773</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>P13</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>DakshinaChitra</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>2010.7</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.0004973392350922564</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.01178741149398649</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>P14</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Cholamandal Artists' Village</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>1372</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.0007288629737609329</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.01727474365230222</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>P15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Vivekananda House</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>323.7</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.003089280197713933</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.07321887022230042</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>P16</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Thousand Lights Mosque</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>296.6</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.003371544167228591</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.07990879396816805</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>P17</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Parthasarathy Temple</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>318.3</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.003141690229343387</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.07446103767187762</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>P18</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Vadapalani Murugan Temple</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>735.7</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.001359249694168819</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.03221550671599652</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>P19</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Express Avenue</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>287.3</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.003480682213713888</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.08249546916449232</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>P20</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>MGM Dizzee World</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>2137.6</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.000467814371257485</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.01108764422294098</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/BayesTrip_Data.xlsx
+++ b/data/BayesTrip_Data.xlsx
@@ -10,6 +10,7 @@
     <sheet name="01_Place_Master" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="07_Coordinates" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="04_HMM_Initial" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="05_HMM_Transition" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1950,4 +1951,1570 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:V21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>from_place_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>from_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>P03</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>P04</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>P06</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>P07</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>P08</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>P09</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>P12</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>P13</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>P14</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>P15</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>P16</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>P17</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>P18</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>P19</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>P20</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Marina Beach</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.06921107093768558</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.06260968889987915</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.08363109079911261</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.05044967268481613</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.02082086166198765</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.009445869758591149</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.0507720703286812</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.02646188757913808</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.06688059656068368</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.03006310740495241</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.02971033593185755</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.01255742615824914</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.01926290905037667</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.1558888059212147</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.06394772554858597</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.1399779192901308</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.02599612491837474</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.07056773511533088</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.011745101450352</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Fort St. George</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0.09487261675032413</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.0556642743301005</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.06673727513770114</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.07394051212540154</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.02599282430608177</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.01334630695812448</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.05886349191773715</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.03140657113554399</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.06705452234017076</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.03246451819126585</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.03215837610262282</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.01533015508522997</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.02239667504260322</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.09200365531879937</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.08605888224911543</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.09350055118719804</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.03544584002173733</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.08833712763743531</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.01442582416280729</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>P03</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kapaleeshwarar Temple</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0.0655870857272516</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.04288686920171556</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.2031780557853618</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.0397091879573156</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.02630032553578173</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.009249208740518159</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.05287105833533403</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.03690043965485043</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.07218525177133675</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.04490192792096456</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.04406820512137105</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.01393947807537366</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.02371563339187872</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.1038856533428762</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.05470574298374862</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.07421933790372492</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.02568112643279899</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.05313118654362597</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.01288422557417166</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>P04</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>San Thome Basilica</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0.08014483026497554</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.04623889843200166</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.1527700573695644</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.03797174836353337</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.02211052246284202</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.008019543739837797</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.04958465943254734</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.03044658167489961</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.06929947673330189</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.03653706588796449</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.03591032262768085</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.01198290738079298</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.02002988766058741</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.1638041801718374</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.05141815426176704</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.0955387470109563</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.02332610034772216</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.05376919603156841</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.01109712014561932</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Government Museum, Chennai</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0.07043898937378749</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.07439669678256217</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.05027594992093272</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.05724745820970006</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.02512067762195036</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.01211781750903794</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.07632994427960006</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.03068964254210412</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.08674563932386321</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.02746696619175635</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.02720092106951581</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.01278530385471788</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.01878925472010154</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.06851277572335149</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.1245383301404001</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.07525107580921703</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.03876708941870465</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.1113034204913332</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.01202204701736374</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>P06</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Guindy National Park</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0.04653491063506334</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.04632455694560299</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.05403702346178824</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.05381108102607675</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.05513531506148982</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.02629570716427528</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.07359930273602518</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.08378397536293312</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.06149496135928139</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.05751331919270144</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.0569744834008209</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.0296487092029024</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.04415840705970103</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.05076070053863266</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.06300013174774287</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.05000389963605072</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.06443045258728294</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.0547317928268394</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.02776127005478947</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>P07</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Arignar Anna Zoological Park (Vandalur Zoo)</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0.0486478687439852</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.05058147870309573</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.04729197375365453</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.04820512587262191</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.05508608804510758</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.05068613454937136</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.05571248154130893</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.05117140151489909</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.0534291001186326</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.04998587125535054</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.04966286418933422</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.05907695113599609</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.06059611622833632</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.04917684895700165</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.05308657496211586</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.04911932977195649</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.06161536551094457</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.05133224059941793</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.05553618454686941</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>P08</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Valluvar Kottam</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0.05041353531546464</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.05193190640420579</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.0528124291563646</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.0577734690711328</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.1150421659740508</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.03609222201877147</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.01413192379367059</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.04039550605531444</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.1101849273193837</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.03223280003590295</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.03190969089256002</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.0147350411477013</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.02182611316475737</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.06391795541100175</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.1045384965437242</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.05731621961271465</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.05988756955192472</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.07101646823306199</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.01384156029829223</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>P09</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Birla Planetarium</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0.04976262257548593</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.0413806669885002</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.06569863876379131</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.0619503476317988</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.04857574835933803</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.07191272515985427</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.0190766782685641</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.05833703706200109</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.06963241022564454</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.0691668055118359</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.06807671557391122</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.02621723175640388</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.04567452425328415</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.05879954461088457</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.05954778908101248</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.0543973091231336</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.04823597444149753</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0.05938585220180743</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.02417137841125097</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Semmozhi Poonga</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0.04569158166885951</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.04373876030564454</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.04893132706836299</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.05611097038587047</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.07360695338726776</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.02274769069697452</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.008342189566886397</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.1647906815541118</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.02884166772436256</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.02507534664327499</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.02476164626596703</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.01008094335583166</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.01568956576120594</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.06602500547604259</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.1884060825718036</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.0556085875080717</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.03324404114777486</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0.07889453129156557</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0.009412427620121457</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Elliot's Beach</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>0.01495847738749461</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.01217976843658306</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.02059148959287547</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.02063983515269258</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.01179753971719406</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.01415441754278658</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.005319436196260419</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.01371448064808099</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.0199969846439998</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.01578491260227332</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.7469461911141101</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.008397587423062593</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.01582425467189959</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.01778443312176452</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.01394372465110528</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.0157479354058783</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0.01062403711447977</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0.01391316864383478</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0.007681325933624065</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>P12</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Besant Nagar Beach</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0.01675290988342221</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.01367465541085158</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.02294671523568692</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.02299960660059187</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.01325002872597938</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.01586373746206899</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.006009069404147782</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.01537669289086512</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.02229594039658614</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.0176655020056296</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.7166728244604317</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.009460164908644847</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.01770891211294719</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.01986794014816023</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.0156305315372139</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.01762469853632312</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0.01194454707434053</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0.01559670328572059</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.00865881992038837</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>P13</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>DakshinaChitra</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>0.02924563254341042</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.02684001019687128</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.03276717267221884</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.03279173293771347</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.02646039899840432</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.03092153624051011</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.02644194597943663</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.02882176131716934</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.03547086292077476</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.02985981078761497</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.04021067704126856</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.03978036064011348</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.071315337438458</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.03119288192133508</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.02843272589470092</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.02983318380569148</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0.02698518770505326</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0.02840716328213888</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0.4042216176771162</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>P14</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Cholamandal Artists' Village</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>0.04571061582774126</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.0404740990096175</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.05410414834223601</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.05416601428721349</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.0396812562943057</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.04959038624829524</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.03395343311635498</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.04476038787842203</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.06122014280060943</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.0471093494822009</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.07538418612208719</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.07399824758847996</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.08309451038069494</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.05023767469663324</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.04389887485253281</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.04704816383461916</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0.04077964482029867</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0.04384261828501568</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0.07094624613264174</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>P15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Vivekananda House</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>0.1425116888244712</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.05850834975749344</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.05872681270635033</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.08560573490000402</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.04489081220366064</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.01682314179627655</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.007203913650604102</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.04783223395988612</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.02169938420079118</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.06381748072036447</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.02496525111585975</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.02464167358394931</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.009822254469905081</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0.01541009978025368</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.06570800996312499</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.2081939713994081</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0.02178408338364493</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0.07269293707265045</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0.009162166511301599</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>P16</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Thousand Lights Mosque</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>0.05959836855911219</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.042425957279368</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.0477647574733679</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.05499754438293369</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.06873162503959952</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.02222869668567391</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.008357324015598298</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.1111835110934698</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.02951900071421844</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.1812443537003138</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.02509915033627652</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.02479343186745023</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.01025419228751775</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.01586295533799098</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.07069913338996973</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.08113522973356141</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0.03091833241223847</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0.1056053189747553</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0.009581116716584116</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>P17</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Parthasarathy Temple</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>0.1311697330414792</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.06284072984623164</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.06319960386699462</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.08068498928069497</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.05182772542900939</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.02005006980695061</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.008681823447107275</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.05504321520039034</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.02494543623982573</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.06620437092742162</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.02797938550439003</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.02764463345588892</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.01155366130367004</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0.01780097206785397</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.1582130038115057</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.07414142526991928</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0.02581523413940959</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0.08140343866259818</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0.01080054869865888</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>P18</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Vadapalani Murugan Temple</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>0.04934309455627826</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.04902303124023754</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.04956482087381316</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.05257203852569594</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.07295615571594165</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.04859689629375775</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.02109784610602655</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.1299321028573631</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.05297465408553707</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.07588633973130858</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.03806703992864262</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.03774664586339044</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.02037425665593218</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.02991180995858821</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.0560522915911245</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.07904643328974967</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.0548101981030053</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0.06288393452619069</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0.01916041009741679</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>P19</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Express Avenue</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>0.06078522822502774</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.05828586248505749</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.04763489881548406</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.05513006972722394</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.1029827608294867</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.02270537000700366</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.00954710984315266</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.07517563060897711</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.02894071181036816</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.09677898005662605</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.02559378030527484</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.02532185572760058</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.0113206855781866</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0.01698235802262148</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.06807335037881324</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.1779177147718613</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.07612555082727236</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0.03008067882203869</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0.01061740315792329</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>P20</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>MGM Dizzee World</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>0.02851529464733541</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.02629525897776664</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.03172720334110696</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.03174944763209145</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.0259429868673647</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.03004942361258944</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.02592584920924119</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.02812566327429361</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.03416308368118846</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.02907869883893503</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.03837167631301262</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.0379927885120516</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.426592940575536</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0.06417728747348082</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.03029685852474086</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.02776747596784301</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0.02905430154941465</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0.02642984008234891</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0.02774392091965878</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/BayesTrip_Data.xlsx
+++ b/data/BayesTrip_Data.xlsx
@@ -12,6 +12,7 @@
     <sheet name="04_HMM_Initial" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="05_HMM_Transition" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="03_BN_CPT" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="06_HMM_Emission" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16479,4 +16480,2645 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I61"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>place_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>slot</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>raw_score</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>probability</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>opening_hours_text</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>source_url</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Marina Beach</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Morning</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>fully open</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>24/7 (open public beach, no gate/entry control)</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>YoMetro / multiple travel guides</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>https://yometro.com/travel-guide/attraction-marina-beach-chennai</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Marina Beach</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Afternoon</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>fully open</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>24/7 (open public beach, no gate/entry control)</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>YoMetro / multiple travel guides</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>https://yometro.com/travel-guide/attraction-marina-beach-chennai</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Marina Beach</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Evening</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>fully open</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>24/7 (open public beach, no gate/entry control)</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>YoMetro / multiple travel guides</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>https://yometro.com/travel-guide/attraction-marina-beach-chennai</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Fort St. George</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Morning</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>partially open</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.3289473684210527</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Mo-Th,Sa-Su 09:00-17:00; Fr off (fort/museum grounds); Fort St. George Museum specifically: Mo-Su 09:00-17:00; Fr off (per OSM/Overpass)</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Chennai Tourism (chennaitourism.travel) and OSM/Overpass-provided data</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>https://chennaitourism.travel/fort-st-george-chennai</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Fort St. George</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Afternoon</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>fully open</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.6578947368421053</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Mo-Th,Sa-Su 09:00-17:00; Fr off (fort/museum grounds); Fort St. George Museum specifically: Mo-Su 09:00-17:00; Fr off (per OSM/Overpass)</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Chennai Tourism (chennaitourism.travel) and OSM/Overpass-provided data</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>https://chennaitourism.travel/fort-st-george-chennai</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Fort St. George</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Evening</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.0131578947368421</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Mo-Th,Sa-Su 09:00-17:00; Fr off (fort/museum grounds); Fort St. George Museum specifically: Mo-Su 09:00-17:00; Fr off (per OSM/Overpass)</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Chennai Tourism (chennaitourism.travel) and OSM/Overpass-provided data</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>https://chennaitourism.travel/fort-st-george-chennai</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>P03</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kapaleeshwarar Temple</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Morning</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>fully open</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Mo-Su 05:00-12:30,16:00-21:30 (most sources: open daily, no weekly closure); one source (Tamil Nadu Tourism) states closed Mondays with hours 05:00-12:00,17:00-21:00</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Multiple travel sites (ciplore.com, indianpanorama.in, ymetro.com) vs. tamilnadutourism.com</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>https://www.tamilnadutourism.com/chennai/temples/kapaleeshwarar-temple.php</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>P03</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kapaleeshwarar Temple</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Afternoon</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>partially open</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Mo-Su 05:00-12:30,16:00-21:30 (most sources: open daily, no weekly closure); one source (Tamil Nadu Tourism) states closed Mondays with hours 05:00-12:00,17:00-21:00</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Multiple travel sites (ciplore.com, indianpanorama.in, ymetro.com) vs. tamilnadutourism.com</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>https://www.tamilnadutourism.com/chennai/temples/kapaleeshwarar-temple.php</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>P03</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kapaleeshwarar Temple</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Evening</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>fully open</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Mo-Su 05:00-12:30,16:00-21:30 (most sources: open daily, no weekly closure); one source (Tamil Nadu Tourism) states closed Mondays with hours 05:00-12:00,17:00-21:00</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Multiple travel sites (ciplore.com, indianpanorama.in, ymetro.com) vs. tamilnadutourism.com</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>https://www.tamilnadutourism.com/chennai/temples/kapaleeshwarar-temple.php</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>P04</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>San Thome Basilica</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Morning</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>fully open</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Mo-Su 05:00-21:00 (general church/visiting hours per trawell.in); Mass times: Mon-Sat 05:45,06:15,11:00,17:45,18:15; Sun 06:00,07:15,08:30,10:00,11:30,17:30,18:00</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>trawell.in</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>https://www.trawell.in/tamilnadu/chennai/san-thome-cathedral-basilica</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>P04</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>San Thome Basilica</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Afternoon</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>fully open</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Mo-Su 05:00-21:00 (general church/visiting hours per trawell.in); Mass times: Mon-Sat 05:45,06:15,11:00,17:45,18:15; Sun 06:00,07:15,08:30,10:00,11:30,17:30,18:00</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>trawell.in</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>https://www.trawell.in/tamilnadu/chennai/san-thome-cathedral-basilica</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>P04</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>San Thome Basilica</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Evening</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>fully open</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Mo-Su 05:00-21:00 (general church/visiting hours per trawell.in); Mass times: Mon-Sat 05:45,06:15,11:00,17:45,18:15; Sun 06:00,07:15,08:30,10:00,11:30,17:30,18:00</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>trawell.in</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>https://www.trawell.in/tamilnadu/chennai/san-thome-cathedral-basilica</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Government Museum, Chennai</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Morning</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>partially open</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.3289473684210527</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Sa-Th 09:30-17:00 (sometimes cited as 09:30-17:30); Fr off</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>trawell.in</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>https://www.trawell.in/tamilnadu/chennai/govt-museum</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Government Museum, Chennai</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Afternoon</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>fully open</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.6578947368421053</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Sa-Th 09:30-17:00 (sometimes cited as 09:30-17:30); Fr off</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>trawell.in</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>https://www.trawell.in/tamilnadu/chennai/govt-museum</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Government Museum, Chennai</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Evening</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.0131578947368421</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Sa-Th 09:30-17:00 (sometimes cited as 09:30-17:30); Fr off</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>trawell.in</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>https://www.trawell.in/tamilnadu/chennai/govt-museum</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>P06</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Guindy National Park</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Morning</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>partially open</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>9:00 AM - 5:30 PM (Wikipedia states 9 AM - 6 PM); closed Tuesdays</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Wikipedia</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Guindy_National_Park</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>P06</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Guindy National Park</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Afternoon</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>fully open</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>9:00 AM - 5:30 PM (Wikipedia states 9 AM - 6 PM); closed Tuesdays</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Wikipedia</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Guindy_National_Park</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>P06</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Guindy National Park</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Evening</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>partially open</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>9:00 AM - 5:30 PM (Wikipedia states 9 AM - 6 PM); closed Tuesdays</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Wikipedia</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Guindy_National_Park</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>P07</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Arignar Anna Zoological Park (Vandalur Zoo)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Morning</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>partially open</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.3289473684210527</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>9:00 AM - 5:00 PM (Wikipedia states 8:30 AM - 5:30 PM); closed Tuesdays</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Wikipedia</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Arignar_Anna_Zoological_Park</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>P07</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Arignar Anna Zoological Park (Vandalur Zoo)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Afternoon</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>fully open</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.6578947368421053</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>9:00 AM - 5:00 PM (Wikipedia states 8:30 AM - 5:30 PM); closed Tuesdays</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Wikipedia</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Arignar_Anna_Zoological_Park</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>P07</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Arignar Anna Zoological Park (Vandalur Zoo)</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Evening</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.0131578947368421</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>9:00 AM - 5:00 PM (Wikipedia states 8:30 AM - 5:30 PM); closed Tuesdays</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Wikipedia</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Arignar_Anna_Zoological_Park</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>P08</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Valluvar Kottam</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Morning</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>partially open</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>10:00 AM - 8:00 PM daily (some sources say 8:30 AM - 5:30 PM or 8 AM - 6 PM); no designated weekly closed day, closed on national holidays</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Chennai Tourism</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>https://chennaitourism.travel/valluvar-kottam-monument-chennai</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>P08</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Valluvar Kottam</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Afternoon</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>fully open</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>10:00 AM - 8:00 PM daily (some sources say 8:30 AM - 5:30 PM or 8 AM - 6 PM); no designated weekly closed day, closed on national holidays</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Chennai Tourism</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>https://chennaitourism.travel/valluvar-kottam-monument-chennai</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>P08</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Valluvar Kottam</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Evening</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>partially open</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>10:00 AM - 8:00 PM daily (some sources say 8:30 AM - 5:30 PM or 8 AM - 6 PM); no designated weekly closed day, closed on national holidays</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Chennai Tourism</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>https://chennaitourism.travel/valluvar-kottam-monument-chennai</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>P09</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Birla Planetarium</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Morning</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>partially open</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Open daily 10:00 AM - 5:45 PM, closed only on national holidays. English 3D/sky show timings: 10:45 AM, 1:15 PM, 3:45 PM. Tamil show timings: 12:00 PM, 2:30 PM, 4:30 PM. Saturday night sky observation show: 7:00 PM - 9:00 PM.</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Wikipedia</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Birla_Planetarium,_Chennai</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>P09</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Birla Planetarium</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Afternoon</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>fully open</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Open daily 10:00 AM - 5:45 PM, closed only on national holidays. English 3D/sky show timings: 10:45 AM, 1:15 PM, 3:45 PM. Tamil show timings: 12:00 PM, 2:30 PM, 4:30 PM. Saturday night sky observation show: 7:00 PM - 9:00 PM.</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Wikipedia</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Birla_Planetarium,_Chennai</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>P09</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Birla Planetarium</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Evening</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>partially open</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Open daily 10:00 AM - 5:45 PM, closed only on national holidays. English 3D/sky show timings: 10:45 AM, 1:15 PM, 3:45 PM. Tamil show timings: 12:00 PM, 2:30 PM, 4:30 PM. Saturday night sky observation show: 7:00 PM - 9:00 PM.</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Wikipedia</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Birla_Planetarium,_Chennai</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Semmozhi Poonga</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Morning</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>partially open</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>10:00 AM - 7:30 PM (Wikipedia states 10 AM - 8 PM) for general visitors, all days except Tuesday. Separate early-morning walkers' slot: 6:00 AM - 8:00 AM (monthly pass holders only, Rs.150).</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Wikipedia</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Semmozhi_Poonga</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Semmozhi Poonga</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Afternoon</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>fully open</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>10:00 AM - 7:30 PM (Wikipedia states 10 AM - 8 PM) for general visitors, all days except Tuesday. Separate early-morning walkers' slot: 6:00 AM - 8:00 AM (monthly pass holders only, Rs.150).</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Wikipedia</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Semmozhi_Poonga</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Semmozhi Poonga</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Evening</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>partially open</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>10:00 AM - 7:30 PM (Wikipedia states 10 AM - 8 PM) for general visitors, all days except Tuesday. Separate early-morning walkers' slot: 6:00 AM - 8:00 AM (monthly pass holders only, Rs.150).</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Wikipedia</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Semmozhi_Poonga</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Elliot's Beach</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Morning</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>fully open</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Open 24 hours, every day</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>YoMetro / myholidayhappiness travel guides</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>https://yometro.com/travel-guide/attraction-elliots-beach-chennai</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Elliot's Beach</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Afternoon</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>fully open</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Open 24 hours, every day</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>YoMetro / myholidayhappiness travel guides</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>https://yometro.com/travel-guide/attraction-elliots-beach-chennai</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Elliot's Beach</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Evening</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>fully open</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Open 24 hours, every day</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>YoMetro / myholidayhappiness travel guides</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>https://yometro.com/travel-guide/attraction-elliots-beach-chennai</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>P12</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Besant Nagar Beach</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Morning</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>fully open</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Open 24 hours, every day</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>myholidayhappiness / Rehlat travel guides</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>https://myholidayhappiness.com/place/tamilnadu/chennai/besant-nagar-beach</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>P12</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Besant Nagar Beach</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Afternoon</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>fully open</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Open 24 hours, every day</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>myholidayhappiness / Rehlat travel guides</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>https://myholidayhappiness.com/place/tamilnadu/chennai/besant-nagar-beach</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>P12</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Besant Nagar Beach</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Evening</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>fully open</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Open 24 hours, every day</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>myholidayhappiness / Rehlat travel guides</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>https://myholidayhappiness.com/place/tamilnadu/chennai/besant-nagar-beach</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>P13</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>DakshinaChitra</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Morning</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>partially open</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Weekdays 10:00 AM - 6:00 PM; Weekends 10:00 AM - 7:00 PM</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>DakshinaChitra official website</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>https://www.dakshinachitra.net/visit-Dakshinachitra</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>P13</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>DakshinaChitra</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Afternoon</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>fully open</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>1</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Weekdays 10:00 AM - 6:00 PM; Weekends 10:00 AM - 7:00 PM</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>DakshinaChitra official website</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>https://www.dakshinachitra.net/visit-Dakshinachitra</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>P13</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>DakshinaChitra</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Evening</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>partially open</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Weekdays 10:00 AM - 6:00 PM; Weekends 10:00 AM - 7:00 PM</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>DakshinaChitra official website</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>https://www.dakshinachitra.net/visit-Dakshinachitra</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>P14</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Cholamandal Artists' Village</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Morning</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>partially open</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>9:30 AM - 6:30 PM, every day of the week</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Chennai Tourism (chennaitourism.travel), corroborated by Trawell and other travel guides</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>https://chennaitourism.travel/cholamandal-artists-village-chennai</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>P14</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Cholamandal Artists' Village</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Afternoon</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>fully open</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>9:30 AM - 6:30 PM, every day of the week</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Chennai Tourism (chennaitourism.travel), corroborated by Trawell and other travel guides</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>https://chennaitourism.travel/cholamandal-artists-village-chennai</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>P14</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Cholamandal Artists' Village</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Evening</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>partially open</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>9:30 AM - 6:30 PM, every day of the week</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Chennai Tourism (chennaitourism.travel), corroborated by Trawell and other travel guides</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>https://chennaitourism.travel/cholamandal-artists-village-chennai</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>P15</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Vivekananda House</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Morning</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>partially open</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>10:00 AM - 12:30 PM and 3:00 PM - 7:15 PM (split morning/evening sessions)</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>IndianHoliday / Chennai Tourism travel guides</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>https://www.indianholiday.com/tamil-nadu/chennai/historical-monuments/vivekananda-illam-chennai.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>P15</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Vivekananda House</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Afternoon</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>partially open</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>10:00 AM - 12:30 PM and 3:00 PM - 7:15 PM (split morning/evening sessions)</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>IndianHoliday / Chennai Tourism travel guides</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>https://www.indianholiday.com/tamil-nadu/chennai/historical-monuments/vivekananda-illam-chennai.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>P15</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Vivekananda House</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Evening</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>partially open</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>10:00 AM - 12:30 PM and 3:00 PM - 7:15 PM (split morning/evening sessions)</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>IndianHoliday / Chennai Tourism travel guides</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>https://www.indianholiday.com/tamil-nadu/chennai/historical-monuments/vivekananda-illam-chennai.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>P16</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Thousand Lights Mosque</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Morning</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>fully open</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>1</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Daily 5:30 AM - 9:00 PM. No formal midday closure to visitors, but avoid the 5 daily prayer times (especially Friday Jumu'ah early afternoon) when access for non-worshippers may be restricted.</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Multiple travel sites (Yatra.com, Holidify, Trawell)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>https://www.yatra.com/india-tourism/attractions-in-chennai/thousand-lights-mosque</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>P16</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Thousand Lights Mosque</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Afternoon</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>fully open</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>1</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Daily 5:30 AM - 9:00 PM. No formal midday closure to visitors, but avoid the 5 daily prayer times (especially Friday Jumu'ah early afternoon) when access for non-worshippers may be restricted.</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Multiple travel sites (Yatra.com, Holidify, Trawell)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>https://www.yatra.com/india-tourism/attractions-in-chennai/thousand-lights-mosque</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>P16</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Thousand Lights Mosque</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Evening</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>fully open</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>1</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Daily 5:30 AM - 9:00 PM. No formal midday closure to visitors, but avoid the 5 daily prayer times (especially Friday Jumu'ah early afternoon) when access for non-worshippers may be restricted.</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Multiple travel sites (Yatra.com, Holidify, Trawell)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>https://www.yatra.com/india-tourism/attractions-in-chennai/thousand-lights-mosque</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>P17</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Parthasarathy Temple</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Morning</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>fully open</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>1</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Daily: morning 6:00 AM - 12:00/12:30 PM, closed midday, reopens evening 4:00 PM - 9:00 PM. Saturday differs: 5:30 AM - 12:00 PM and 4:00 PM - 10:00 PM.</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>GoTirupati / Trawell / DarshansTime (temple info aggregators)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>https://gotirupati.com/parthasarathy-temple-triplicane/</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>P17</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Parthasarathy Temple</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Afternoon</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>partially open</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Daily: morning 6:00 AM - 12:00/12:30 PM, closed midday, reopens evening 4:00 PM - 9:00 PM. Saturday differs: 5:30 AM - 12:00 PM and 4:00 PM - 10:00 PM.</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>GoTirupati / Trawell / DarshansTime (temple info aggregators)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>https://gotirupati.com/parthasarathy-temple-triplicane/</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>P17</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Parthasarathy Temple</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Evening</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>fully open</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>1</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Daily: morning 6:00 AM - 12:00/12:30 PM, closed midday, reopens evening 4:00 PM - 9:00 PM. Saturday differs: 5:30 AM - 12:00 PM and 4:00 PM - 10:00 PM.</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>GoTirupati / Trawell / DarshansTime (temple info aggregators)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>https://gotirupati.com/parthasarathy-temple-triplicane/</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>P18</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Vadapalani Murugan Temple</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Morning</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>fully open</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>1</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Daily: 5:00 AM - 12:30 PM, closed midday, reopens 4:00 PM - 9:00 PM. Same schedule Monday to Sunday; extended/continuous hours during festival days.</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>GoTirupati / DarshansBooking (temple info aggregators)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>https://gotirupati.com/vadapalani-temple-timings/</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>P18</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Vadapalani Murugan Temple</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Afternoon</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>partially open</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Daily: 5:00 AM - 12:30 PM, closed midday, reopens 4:00 PM - 9:00 PM. Same schedule Monday to Sunday; extended/continuous hours during festival days.</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>GoTirupati / DarshansBooking (temple info aggregators)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>https://gotirupati.com/vadapalani-temple-timings/</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>P18</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Vadapalani Murugan Temple</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Evening</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>fully open</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>1</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Daily: 5:00 AM - 12:30 PM, closed midday, reopens 4:00 PM - 9:00 PM. Same schedule Monday to Sunday; extended/continuous hours during festival days.</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>GoTirupati / DarshansBooking (temple info aggregators)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>https://gotirupati.com/vadapalani-temple-timings/</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>P19</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Express Avenue</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Morning</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>partially open</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Daily 10:00 AM - 10:00 PM, same hours every day of the week including weekends and public holidays.</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Holidify / Rehlat / malls.com (travel/mall aggregator sites)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>https://www.holidify.com/places/chennai/express-avenue-sightseeing-121150.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>P19</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Express Avenue</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Afternoon</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>fully open</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>1</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Daily 10:00 AM - 10:00 PM, same hours every day of the week including weekends and public holidays.</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Holidify / Rehlat / malls.com (travel/mall aggregator sites)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>https://www.holidify.com/places/chennai/express-avenue-sightseeing-121150.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>P19</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Express Avenue</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Evening</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>fully open</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>1</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Daily 10:00 AM - 10:00 PM, same hours every day of the week including weekends and public holidays.</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Holidify / Rehlat / malls.com (travel/mall aggregator sites)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>https://www.holidify.com/places/chennai/express-avenue-sightseeing-121150.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>P20</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>MGM Dizzee World</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Morning</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>partially open</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Mo-Fr 10:30 AM - 6:00 PM; Sa-Su and Public Holidays 10:30 AM - 6:30 PM. Extended to ~7:30 PM during peak summer (mid-April to end May) and winter (mid-December to end January) seasons.</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Official site (mgmdizzeeworld.com) and NativePlanet</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>https://www.mgmdizzeeworld.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>P20</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>MGM Dizzee World</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Afternoon</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>fully open</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Mo-Fr 10:30 AM - 6:00 PM; Sa-Su and Public Holidays 10:30 AM - 6:30 PM. Extended to ~7:30 PM during peak summer (mid-April to end May) and winter (mid-December to end January) seasons.</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Official site (mgmdizzeeworld.com) and NativePlanet</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>https://www.mgmdizzeeworld.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>P20</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>MGM Dizzee World</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Evening</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>partially open</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Mo-Fr 10:30 AM - 6:00 PM; Sa-Su and Public Holidays 10:30 AM - 6:30 PM. Extended to ~7:30 PM during peak summer (mid-April to end May) and winter (mid-December to end January) seasons.</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Official site (mgmdizzeeworld.com) and NativePlanet</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>https://www.mgmdizzeeworld.com/</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/BayesTrip_Data.xlsx
+++ b/data/BayesTrip_Data.xlsx
@@ -14,6 +14,7 @@
     <sheet name="03_BN_CPT" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="06_HMM_Emission" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="08_Evidence" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="09_Validation" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -33233,4 +33234,137 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>check</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>detail</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>01_Place_Master has exactly 20 places</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>found 20 rows</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>02_BN_Prior sums to 1</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>sheet not found (pending: needs OpenTripMap API key)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>03_BN_CPT: each (place, variable) sums to 1</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>all groups OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>05_HMM_Transition: each row sums to 1</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>max error=2.22e-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>06_HMM_Emission: each place sums to 1</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>max error=0.00e+00</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>04_HMM_Initial: pi sums to 1</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>sum=1.000000</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/BayesTrip_Data.xlsx
+++ b/data/BayesTrip_Data.xlsx
@@ -15,6 +15,7 @@
     <sheet name="06_HMM_Emission" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="08_Evidence" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="09_Validation" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="02_BN_Prior" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19131,7 +19132,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G381"/>
+  <dimension ref="A1:G401"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33228,6 +33229,746 @@
       <c r="G381" t="inlineStr">
         <is>
           <t>2026-09-08T11:18:21.717231+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>step03_bn_prior</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>popularity</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>Holidify page for Marina Beach, Chennai shows a 4.3 out of 5 star rating based on 82 votes.</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>Holidify</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>https://www.holidify.com/places/chennai/marina-beach-sightseeing-1547.html</t>
+        </is>
+      </c>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>2026-09-10T09:31:25.008379+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>step03_bn_prior</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>popularity</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>Wanderlog's page for Fort St. George Museum (the museum inside the Fort St. George complex, the part of the fort open to visitors) shows two ratings: Google Maps 4.3/5 based on 6,123 reviews, and Tripadvisor 3.6/5 based on 167 reviews.</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>Google Maps (via Wanderlog)</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>https://wanderlog.com/place/details/36091/fort-st-george-museum</t>
+        </is>
+      </c>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>2026-09-10T09:31:25.009741+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>step03_bn_prior</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>P03</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>popularity</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>Wanderlog's page for Kapaleeshwarar Temple shows a Google Maps rating of 4.8 out of 5 based on 11,037 reviews.</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>Google Maps (via Wanderlog)</t>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>https://wanderlog.com/place/details/4449403/kapaleeshwarar-temple</t>
+        </is>
+      </c>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>2026-09-10T09:31:25.010752+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>step03_bn_prior</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>P04</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>popularity</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>Wanderlog's page for Santhome Cathedral Basilica shows a Google Maps rating of 4.7 out of 5 based on 16,903 reviews.</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>Google Maps (via Wanderlog)</t>
+        </is>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>https://wanderlog.com/place/details/14401262/santhome-cathedral-basilica</t>
+        </is>
+      </c>
+      <c r="G385" t="inlineStr">
+        <is>
+          <t>2026-09-10T09:31:25.010752+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>step03_bn_prior</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>popularity</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>A WebSearch query for the Tripadvisor listing reported: 'The Government Museum in Chennai has a rating of 3.7 out of 5 bubbles based on 373 reviews and is ranked #41 of 477 things to do in Chennai.'</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>Tripadvisor</t>
+        </is>
+      </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>https://www.tripadvisor.in/Attraction_Review-g304556-d325410-Reviews-Government_Museum-Chennai_Madras_Chennai_District_Tamil_Nadu.html</t>
+        </is>
+      </c>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t>2026-09-10T09:31:25.011753+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>step03_bn_prior</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>P06</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>popularity</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>A Google search summary (Google Maps listing) reported: 'Guindy National Park has a rating of 4.1 stars with "Very good" status based on 25,388 reviews on Google Maps.' Tripadvisor listing (g304556-d2651336) exists with many individual reviews but the numeric aggregate rating/review-count was not visible in normal search snippets (direct page fetch returned HTTP 403). Justdial also lists the park with a rating of approximately 4.2 based on ~27,000-29,000 ratings, but the exact count was inconsistent across two separate lookups (27,872 vs 29,084), so it was not used as primary.</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>Google Maps</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Guindy+National+Park/@13.0049251,80.2378725,17z/data=!3m1!4b1!4m5!3m4!1s0x3a526779bf1f61f3:0xeaabf055ed85268d!8m2!3d13.0049251!4d80.2378725</t>
+        </is>
+      </c>
+      <c r="G387" t="inlineStr">
+        <is>
+          <t>2026-09-10T09:31:25.011753+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>step03_bn_prior</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>P07</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>popularity</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>Justdial listing title and summary: 'Arignar Anna Zoological Park Reviews, Vandalur, Chennai - 72,016 Ratings - Justdial', with a rating of 4.2 out of 5. Tripadvisor listing (g304556-d3613690) confirms the attraction has 478 individual written reviews and is ranked #23 of 475 things to do in Chennai, but no numeric star/bubble rating was visible in search snippets or the (403-blocked) page fetch. MouthShut separately lists 3.27/5 for this attraction (different, smaller user base).</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>Justdial</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>https://www.justdial.com/Chennai/Arignar-Anna-Zoological-Park-Near-Crescent-Engineering-College-Vandalur/044P3034815_BZDET/reviews</t>
+        </is>
+      </c>
+      <c r="G388" t="inlineStr">
+        <is>
+          <t>2026-09-10T09:31:25.012750+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>step03_bn_prior</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>P08</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>popularity</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>Web search summary for the Tripadvisor listing (g304556-d2665502) reported: 'Valluvar Kottam Monument has a rating of 3.3 out of 5 bubbles on TripAdvisor, based on 88 reviews.' Direct page fetch was blocked (HTTP 403), so this is taken from the search-result summary of the live page rather than independently re-verified. Justdial separately lists Valluvar Kottam at 4.1/5 based on roughly 3,295-3,477 ratings (different platform, larger sample, numbers varied slightly between two lookups).</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>Tripadvisor</t>
+        </is>
+      </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>https://www.tripadvisor.com/Attraction_Review-g304556-d2665502-Reviews-Valluvar_Kottam_Monument-Chennai_Madras_Chennai_District_Tamil_Nadu.html</t>
+        </is>
+      </c>
+      <c r="G389" t="inlineStr">
+        <is>
+          <t>2026-09-10T09:31:25.012750+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>step03_bn_prior</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>P09</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>popularity</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>A Google search summary reported: 'the average rating of this place is 4.10 out of 5 stars based on 2556 reviews' for B.M. Birla Planetarium, Chennai. Tripadvisor listing (g304556-d325397, 'B M Birla Planaturium') separately shows 125 traveler reviews with mixed sentiment (praise for the 3D show, criticism of maintenance), but no numeric aggregate rating was visible in search snippets (direct fetch returned HTTP 403). Justdial lists 3,155 ratings for this location without a clearly stated score in search snippets.</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>Google Maps</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>https://www.google.com/travel/hotels/entity/ChcIkcbvwsC2rtXIARoKL20vMGRsa253cxAE</t>
+        </is>
+      </c>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t>2026-09-10T09:31:25.013737+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>step03_bn_prior</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>popularity</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>Web search summary stated: 'On MouthShut, it is rated 3.5/5 by users' for Semmozhi Poonga, but no total review count was given in the snippet. Tripadvisor listing (g304556-d8015909) shows the park ranked #60 of 475 things to do in Chennai with 70 reviews, but no reliable numeric star/bubble rating could be confirmed (one search summary claimed '5.0 out of 5 bubbles', which is not credible as an aggregate score and was discarded as likely a misread of a single 5-bubble review rather than the overall rating; direct page fetch was blocked with HTTP 403). A Justdial result for 'Semmozhi Poonga Parking' showed 3.8/5 from 45 ratings, but this appears to be a sub-listing for the parking area rather than the garden itself, so it was not used.</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>MouthShut</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>https://www.mouthshut.com/product-reviews/semmozhi-poonga-chennai-reviews-925970096</t>
+        </is>
+      </c>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>2026-09-10T09:31:25.013737+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>step03_bn_prior</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>popularity</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>Wanderlog's aggregator page for 'Edward Elliot's Beach' (Besant Nagar, Chennai) displays: Tripadvisor 4.1 out of 5 stars from 2,107 reviews; Google 4.4 out of 5 stars from 8,282 reviews. A direct web_search of Tripadvisor also independently surfaced a review snippet citing '2,109 traveler reviews and 614 candid photos' for the Besant Nagar Beach / Edward Elliot's Beach Tripadvisor listing, corroborating the ~2,100 review count.</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>Tripadvisor (via Wanderlog aggregator page, since Tripadvisor's own pages returned HTTP 403 to direct fetch)</t>
+        </is>
+      </c>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>https://wanderlog.com/place/details/23996/edward-elliots-beach</t>
+        </is>
+      </c>
+      <c r="G392" t="inlineStr">
+        <is>
+          <t>2026-09-10T09:31:25.014738+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>step03_bn_prior</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>P12</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>popularity</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>Wanderlog's page specifically titled 'Besant Nagar Beach' shows Google rating 4.5/5 from 41,541 reviews, but does not surface a distinct Tripadvisor number on that page (only a link to 'All Tripadvisor reviews'). Because Tripadvisor itself (and most travel sites) list Besant Nagar Beach and Edward Elliot's Beach as the same physical attraction/listing, the Tripadvisor figure of 4.1/5 from 2,107 reviews found for P11 is reused here per task instructions allowing identical numbers for this same-place duplicate entry. The much larger Google figure (4.5/5, 41,541 reviews) is recorded separately below in evidence_text for transparency but not used as the primary rating field to keep the source consistent with P11 (Tripadvisor).</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>Tripadvisor (via Wanderlog aggregator page)</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>https://wanderlog.com/place/details/13377030/besant-nagar-beach</t>
+        </is>
+      </c>
+      <c r="G393" t="inlineStr">
+        <is>
+          <t>2026-09-10T09:31:25.014738+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>step03_bn_prior</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>P13</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>popularity</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>Holidify's page for Dakshinachitra Museum shows a rating of 3.0 out of 5 stars based on 33 votes, ranked #9 among Things To Do in Chennai. Note: Tripadvisor's own listing (g303893-d2062837, 'DakshinaChitra Museum', Muttukadu) could not be fetched directly (HTTP 403), but a normal web_search surfaced a review-category breakdown for that listing of 416 total reviews (217 Excellent, 155 Very good, 34 Average, 6 Poor, 4 Terrible), which is qualitatively much more positive than Holidify's 3.0/5 -- this discrepancy across sources is reported as-is rather than resolved by computing our own average. Justdial search-snippet summaries claimed a 4.3 rating from 19,059 reviews, but this number could not be verified from the Justdial page itself (fetch returned HTTP 403) and the review count seems implausibly high for a single heritage museum, so it was not used.</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>Holidify</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>https://www.holidify.com/places/chennai/dakshinachitra-museum-sightseeing-120674.html</t>
+        </is>
+      </c>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>2026-09-10T09:31:25.015740+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>step03_bn_prior</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>P14</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>popularity</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>Wanderlog's aggregator page for Cholamandal Artists' Village displays the Tripadvisor badge '4.2 (65)' in multiple places, i.e. 4.2 out of 5 stars from 65 reviews. This matches an independent web_search finding that stated 'Cholamandal Artists' Village has 65 reviews on Tripadvisor and is ranked #58 of 464 things to do in Chennai,' corroborating the review count.</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>Tripadvisor (via Wanderlog aggregator page)</t>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>https://wanderlog.com/place/details/550762/cholamandal-artists-village</t>
+        </is>
+      </c>
+      <c r="G395" t="inlineStr">
+        <is>
+          <t>2026-09-10T09:31:25.015740+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>step03_bn_prior</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>P15</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>popularity</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>Wanderlog's aggregator page for Vivekananda House shows: Tripadvisor 4.4 out of 5 stars from 192 reviews; Google 4.5 out of 5 stars from 10,308 reviews. Google's figure (10,308 reviews) is included here for reference but Tripadvisor was used as the primary source per task preference. A Justdial search-snippet summary claimed a 4.5 rating from 9,677 reviews, but this could not be verified directly (Justdial page fetch returned HTTP 403), so it was not used.</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>Tripadvisor (via Wanderlog aggregator page)</t>
+        </is>
+      </c>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>https://wanderlog.com/place/details/36243/vivekananda-house</t>
+        </is>
+      </c>
+      <c r="G396" t="inlineStr">
+        <is>
+          <t>2026-09-10T09:31:25.016741+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>step03_bn_prior</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>P16</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>popularity</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>A web search snippet reported: 'On Justdial, the Thousand Lights Mosque on Anna Salai in Thousand Lights, Chennai has a rating of 4.4 out of 5 with 1,688 ratings.' Tripadvisor's own attraction page (g304556-d3705587) exists with about 10 user reviews visible in search results, but its aggregate bubble rating did not appear in any search snippet or accessible page (direct fetch of tripadvisor.com returned HTTP 403).</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>Justdial</t>
+        </is>
+      </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>https://www.justdial.com/Chennai/Mosques-in-Thousand-Lights/nct-10328437</t>
+        </is>
+      </c>
+      <c r="G397" t="inlineStr">
+        <is>
+          <t>2026-09-10T09:31:25.017253+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>step03_bn_prior</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>P17</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>popularity</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>Direct Tripadvisor search results confirmed the temple is 'ranked #4 of 463 things to do in Chennai (Madras)' with 812-813 Reviews, but did not show the bubble rating value. Fetching Wanderlog's aggregation page (which displays both Google and Tripadvisor scores with source icons) showed: Tripadvisor 4.5/5 with 813 reviews; Google 4.7/5 with 28,398 reviews. Direct fetch of the tripadvisor.com attraction page itself returned HTTP 403.</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>Tripadvisor (rating/count surfaced via Wanderlog listing page)</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>https://wanderlog.com/place/details/656/arulmigu-sri-parthasarathyswamy-temple</t>
+        </is>
+      </c>
+      <c r="G398" t="inlineStr">
+        <is>
+          <t>2026-09-10T09:31:25.017253+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>step03_bn_prior</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>P18</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>popularity</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>Direct Tripadvisor search results did not show a bubble rating value in snippets. Wanderlog's aggregation page displayed: Tripadvisor 4.5/5 with 469 reviews; Google 4.7/5 with 32,645 reviews. A separate Justdial listing ('Arulmigu Vadapalani Andavar Thirukovil') showed 4.5/5 from a much smaller base (34 ratings), which was disregarded in favor of the larger, more representative Tripadvisor/Google figures. Direct fetch of tripadvisor.com returned HTTP 403.</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>Tripadvisor (rating/count surfaced via Wanderlog listing page)</t>
+        </is>
+      </c>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>https://wanderlog.com/place/details/665/arulmigu-vadapalani-murugan-temple</t>
+        </is>
+      </c>
+      <c r="G399" t="inlineStr">
+        <is>
+          <t>2026-09-10T09:31:25.017253+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>step03_bn_prior</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>P19</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>popularity</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>Direct Tripadvisor search results repeatedly confirmed '942-949 traveler reviews' but never displayed the bubble rating value in snippets. Wanderlog's aggregation page displayed: Tripadvisor 4.2/5 with 944 reviews; Google Maps 4.4/5 with 105,447 reviews. Direct fetch of tripadvisor.com returned HTTP 403.</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>Tripadvisor (rating/count surfaced via Wanderlog listing page)</t>
+        </is>
+      </c>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>https://wanderlog.com/place/details/24157/express-avenue</t>
+        </is>
+      </c>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>2026-09-10T09:31:25.018269+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>step03_bn_prior</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>P20</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>popularity</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>Tripadvisor search results showed only ~138-139 reviews with a review-band breakdown (Excellent 33, Very good 46, Average 37, Poor 9) but no aggregate bubble rating value appeared in any snippet, and direct fetch of tripadvisor.com returned HTTP 403. Wanderlog's aggregation page explicitly stated '4.0 (24536)' next to a Google Maps icon, i.e. a Google rating of 4.0/5 from 24,536 reviews. A MouthShut listing separately showed 2.92/5, but was not used since it is a much smaller/less standard sample and Google's figure is far more representative and directly comparable in scale to the other places' Google figures.</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>Google (rating/count surfaced via Wanderlog listing page)</t>
+        </is>
+      </c>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>https://wanderlog.com/place/details/895947/mgm-dizzee-world</t>
+        </is>
+      </c>
+      <c r="G401" t="inlineStr">
+        <is>
+          <t>2026-09-10T09:31:25.019283+00:00</t>
         </is>
       </c>
     </row>
@@ -33287,12 +34028,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>sheet not found (pending: needs OpenTripMap API key)</t>
+          <t>sum=1.000000</t>
         </is>
       </c>
     </row>
@@ -33361,6 +34102,1054 @@
       <c r="C7" t="inlineStr">
         <is>
           <t>sum=1.000000</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>place_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>place_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>rating</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>review_count</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>popularity_score</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>prior_probability</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>justification</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>source_url</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>confidence</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>retrieved_at</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Marina Beach</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="D2" t="n">
+        <v>82</v>
+      </c>
+      <c r="E2" t="n">
+        <v>19.00101461352537</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.03266232019962672</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Source states: 4.3/5 based on 82 votes (directly fetched page). Note: Tripadvisor also lists Marina Beach with a large review volume (search snippets suggested figures ranging from ~4,000 to ~62,000+ reviews across different aggregators/listings, e.g. Justdial shows 62,855 ratings), but attempts to fetch Tripadvisor's own attraction page directly returned HTTP 403 (blocked), and WebSearch summaries for the Tripadvisor rating were inconsistent/contradictory across queries (e.g. one search reported 3.8/5 with 4,022 reviews, which could not be verified against the actual page), so those numbers were not used. The Holidify figure is the only number confirmed via a directly and successfully fetched public page.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Holidify</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>https://www.holidify.com/places/chennai/marina-beach-sightseeing-1547.html</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2026-09-10T09:31:25.027062+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Fort St. George</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="D3" t="n">
+        <v>6123</v>
+      </c>
+      <c r="E3" t="n">
+        <v>37.49587425414357</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.06445457129336687</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Source states: Google Maps rating 4.3 out of 5 with 6,123 reviews (directly fetched page, listing both Google and Tripadvisor figures side by side). A separate WebSearch also independently reported Fort St. George on Tripadvisor as '3.6 out of 5 bubbles with 230 reviews,' consistent in the rating value (3.6) though the review count differed slightly (230 vs 167), likely because 'Fort St. George' and 'Fort St. George Museum' are sometimes listed as separate/overlapping Tripadvisor entries. Google Maps figure (4.3/6123) was chosen as primary because it came from a directly fetched, larger-sample listing.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Google Maps (via Wanderlog)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>https://wanderlog.com/place/details/36091/fort-st-george-museum</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2026-09-10T09:31:25.027062+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>P03</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kapaleeshwarar Temple</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="D4" t="n">
+        <v>11037</v>
+      </c>
+      <c r="E4" t="n">
+        <v>44.68367589119735</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.07681024194443499</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Source states: 4.8/5 based on 11,037 reviews, sourced from Google Maps and displayed on a directly fetched public page. Tripadvisor separately lists Kapaleeshwarar Temple with 2,589-2,590 reviews and is ranked #4-5 of ~476 things to do in Chennai (via WebSearch), but a specific Tripadvisor star rating could not be reliably confirmed (one search result implausibly reported '5.05 of 5 bubbles', which is not a valid Tripadvisor scale value and was discarded as an unreliable/garbled search summary). The Google Maps figure via Wanderlog is used as it was directly verified on a successfully fetched page.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Google Maps (via Wanderlog)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>https://wanderlog.com/place/details/4449403/kapaleeshwarar-temple</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2026-09-10T09:31:25.027062+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>P04</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>San Thome Basilica (Santhome Cathedral Basilica)</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="D5" t="n">
+        <v>16903</v>
+      </c>
+      <c r="E5" t="n">
+        <v>45.7559361286907</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.07865343337008686</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Source states: 4.7/5 based on 16,903 reviews, sourced from Google Maps and displayed on a directly fetched public page. This is corroborated by Tripadvisor, which a WebSearch reported as showing '4.4 of 5 bubbles based on 1,262 reviews, ranked #8 of 477 things to do in Chennai' -- a consistent, plausible figure though not independently fetched from the live Tripadvisor page (blocked with 403). Both sources agree the attraction is highly rated; the Google Maps figure is used as primary since it was directly confirmed on a fetched page.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Google Maps (via Wanderlog)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>https://wanderlog.com/place/details/14401262/santhome-cathedral-basilica</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2026-09-10T09:31:25.027062+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Government Museum, Chennai (Egmore)</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D6" t="n">
+        <v>373</v>
+      </c>
+      <c r="E6" t="n">
+        <v>21.91974645043377</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.03767955510907661</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Source states: 3.7/5 based on 373 reviews. IMPORTANT CAVEAT: direct fetches of the live Tripadvisor page returned HTTP 403 (blocked) for this and every other place, so this number comes only from a WebSearch results summary rather than a directly verified page load, and could not be cross-checked against the raw page. Other sources gave partial, non-comparable signals: a directly fetched Mappls.com listing showed 4.0/5 from only 6 reviews (too small a sample to be reliable), and Justdial listings (not directly fetchable, 403) mentioned '4-star rating' alongside review-count listings of 17,644 and 19,694 ratings but without a precise decimal value. Given the inconsistency across sources and inability to directly verify any of them, this entry is reported with reduced confidence.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Tripadvisor</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>https://www.tripadvisor.in/Attraction_Review-g304556-d325410-Reviews-Government_Museum-Chennai_Madras_Chennai_District_Tamil_Nadu.html</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2026-09-10T09:31:25.027062+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>P06</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Guindy National Park</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>25388</v>
+      </c>
+      <c r="E7" t="n">
+        <v>41.58249228218668</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.07147937650932089</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Source states: Google Maps rating 4.1/5 based on 25,388 reviews, surfaced consistently via a dedicated web search for the listing.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Google Maps</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Guindy+National+Park/@13.0049251,80.2378725,17z/data=!3m1!4b1!4m5!3m4!1s0x3a526779bf1f61f3:0xeaabf055ed85268d!8m2!3d13.0049251!4d80.2378725</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2026-09-10T09:31:25.027062+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>P07</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Arignar Anna Zoological Park (Vandalur Zoo)</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D8" t="n">
+        <v>72016</v>
+      </c>
+      <c r="E8" t="n">
+        <v>46.97556142120574</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.08074994203754157</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Source states: Justdial rating 4.2/5 based on 72,016 ratings, the most numerous and specific figure found across sources for this place.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Justdial</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>https://www.justdial.com/Chennai/Arignar-Anna-Zoological-Park-Near-Crescent-Engineering-College-Vandalur/044P3034815_BZDET/reviews</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2026-09-10T09:31:25.027062+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>P08</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Valluvar Kottam</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D9" t="n">
+        <v>88</v>
+      </c>
+      <c r="E9" t="n">
+        <v>14.81250002011606</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.02546235706116557</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Source states: Tripadvisor rating 3.3/5 based on 88 reviews, per the search engine's summary of the live Tripadvisor page (preferred per task instructions to favor Tripadvisor when accessible via normal search).</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Tripadvisor</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>https://www.tripadvisor.com/Attraction_Review-g304556-d2665502-Reviews-Valluvar_Kottam_Monument-Chennai_Madras_Chennai_District_Tamil_Nadu.html</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2026-09-10T09:31:25.027062+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>P09</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Birla Planetarium (Chennai)</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2556</v>
+      </c>
+      <c r="E10" t="n">
+        <v>32.17101889869386</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.05530126373722229</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Source states: Google Maps rating 4.1/5 based on 2,556 reviews, the most specific and complete figure found for this place.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Google Maps</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>https://www.google.com/travel/hotels/entity/ChcIkcbvwsC2rtXIARoKL20vMGRsa253cxAE</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>2026-09-10T09:31:25.027062+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Semmozhi Poonga</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.006016421913455042</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Source states: MouthShut rating 3.5/5 (no review count disclosed in the search snippet); review_count left null because no reliable count could be attributed specifically to this attraction's overall garden listing across the sources checked.</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>MouthShut</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>https://www.mouthshut.com/product-reviews/semmozhi-poonga-chennai-reviews-925970096</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2026-09-10T09:31:25.027062+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Elliot's Beach (Besant Nagar)</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2107</v>
+      </c>
+      <c r="E12" t="n">
+        <v>31.37932912961114</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.0539403666871173</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Source states: Tripadvisor 4.1/5 from 2,107 reviews (Wanderlog aggregator, cross-checked against an independent Tripadvisor search snippet showing ~2,109 reviews for the same listing).</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Tripadvisor (via Wanderlog aggregator page, since Tripadvisor's own pages returned HTTP 403 to direct fetch)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>https://wanderlog.com/place/details/23996/edward-elliots-beach</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2026-09-10T09:31:25.027062+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>P12</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Besant Nagar Beach</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2107</v>
+      </c>
+      <c r="E13" t="n">
+        <v>31.37932912961114</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.0539403666871173</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Source states: same Tripadvisor listing/attraction as P11 (Elliot's Beach) -&gt; 4.1/5 from 2,107 reviews; Google Maps listing separately shows 4.5/5 from 41,541 reviews (noted in evidence_text, not used as primary value).</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Tripadvisor (via Wanderlog aggregator page)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>https://wanderlog.com/place/details/13377030/besant-nagar-beach</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>2026-09-10T09:31:25.027062+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>P13</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>DakshinaChitra</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" t="n">
+        <v>33</v>
+      </c>
+      <c r="E14" t="n">
+        <v>10.57908157384848</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.01818520520146585</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Source states: Holidify -- 'Dakshinachitra Museum has a rating of 3.0 out of 5 stars, based on 33 votes.' Used as the primary reported figure since it is a directly confirmed number from a normally-loadable public page; conflicting/unverifiable figures from Tripadvisor (review-breakdown only, page itself blocked) and Justdial (blocked, implausible count) are recorded in evidence_text but not used as the headline number.</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Holidify</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>https://www.holidify.com/places/chennai/dakshinachitra-museum-sightseeing-120674.html</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>2026-09-10T09:31:25.027062+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>P14</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Cholamandal Artists' Village</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D15" t="n">
+        <v>65</v>
+      </c>
+      <c r="E15" t="n">
+        <v>17.59654991651099</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.03024807671968634</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Source states: Tripadvisor 4.2 out of 5 stars from 65 reviews (Wanderlog aggregator page, cross-checked with an independent Tripadvisor search snippet confirming the 65-review count).</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Tripadvisor (via Wanderlog aggregator page)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>https://wanderlog.com/place/details/550762/cholamandal-artists-village</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>2026-09-10T09:31:25.027062+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>P15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Vivekananda House (Vivekanandar Illam)</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="D16" t="n">
+        <v>192</v>
+      </c>
+      <c r="E16" t="n">
+        <v>23.1558368311815</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.03980436689585992</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Source states: Tripadvisor 4.4 out of 5 stars from 192 reviews (Wanderlog aggregator page).</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Tripadvisor (via Wanderlog aggregator page)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>https://wanderlog.com/place/details/36243/vivekananda-house</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>2026-09-10T09:31:25.027062+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>P16</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Thousand Lights Mosque</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1688</v>
+      </c>
+      <c r="E17" t="n">
+        <v>32.70032443395432</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.05621112814329489</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Source states a Justdial rating of 4.4/5 from 1,688 ratings. Used as the best available numeric substitute since Tripadvisor's own aggregate rating could not be retrieved without bypassing its access restrictions.</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Justdial</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>https://www.justdial.com/Chennai/Mosques-in-Thousand-Lights/nct-10328437</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>2026-09-10T09:31:25.027062+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>P17</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Parthasarathy Temple</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D18" t="n">
+        <v>813</v>
+      </c>
+      <c r="E18" t="n">
+        <v>30.15882164701143</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.0518423415545891</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Source states Tripadvisor rating of 4.5/5 based on 813 reviews (cross-checked against Tripadvisor's own review count of ~812 found in direct search results).</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Tripadvisor (rating/count surfaced via Wanderlog listing page)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>https://wanderlog.com/place/details/656/arulmigu-sri-parthasarathyswamy-temple</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>2026-09-10T09:31:25.027062+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>P18</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Vadapalani Murugan Temple</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D19" t="n">
+        <v>469</v>
+      </c>
+      <c r="E19" t="n">
+        <v>27.68729712616847</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.04759384604406308</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Source states Tripadvisor rating of 4.5/5 based on 469 reviews.</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Tripadvisor (rating/count surfaced via Wanderlog listing page)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>https://wanderlog.com/place/details/665/arulmigu-vadapalani-murugan-temple</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>2026-09-10T09:31:25.027062+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>P19</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Express Avenue (shopping mall)</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D20" t="n">
+        <v>944</v>
+      </c>
+      <c r="E20" t="n">
+        <v>28.77497669547372</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.0494635429570875</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Source states Tripadvisor rating of 4.2/5 based on 944 reviews (consistent with the ~942-949 review count independently found via Tripadvisor search snippets).</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Tripadvisor (rating/count surfaced via Wanderlog listing page)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>https://wanderlog.com/place/details/24157/express-avenue</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>2026-09-10T09:31:25.027062+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>P20</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>MGM Dizzee World</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>4</v>
+      </c>
+      <c r="D21" t="n">
+        <v>24536</v>
+      </c>
+      <c r="E21" t="n">
+        <v>40.43174984561234</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.06950127593442131</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Tripadvisor's own aggregate rating was not accessible via normal search/fetch, so Google's publicly surfaced rating (4.0/5, 24,536 reviews) was used as the reliable alternate source.</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Google (rating/count surfaced via Wanderlog listing page)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>https://wanderlog.com/place/details/895947/mgm-dizzee-world</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>2026-09-10T09:31:25.027062+00:00</t>
         </is>
       </c>
     </row>

--- a/data/BayesTrip_Data.xlsx
+++ b/data/BayesTrip_Data.xlsx
@@ -1002,7 +1002,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:N21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1013,22 +1013,67 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>place_name</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>lat</t>
+          <t>search_query</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>lng</t>
+          <t>formatted_address</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>state</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>latitude</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>longitude</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>source</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>source_url</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>retrieved_at</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>confidence</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>justification</t>
         </is>
       </c>
     </row>
@@ -1043,15 +1088,58 @@
           <t>Marina Beach</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Marina Beach, Chennai, Tamil Nadu, India</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Marina Beach, Zone 9 Teynampet, Chennai, India</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Tamil Nadu</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
         <v>13.0532752</v>
       </c>
-      <c r="D2" t="n">
+      <c r="I2" t="n">
         <v>80.28331059999999</v>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>OSM Nominatim</t>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Geoapify Geocoding API</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>https://api.geoapify.com/v1/geocode/search?text=Marina Beach, Chennai, Tamil Nadu, India&amp;filter=circle:80.2763077,13.0825901,30000&amp;bias=proximity:80.2763077,13.0825901&amp;limit=5&amp;format=json</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>2026-09-14T04:15:18.389382+00:00</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Selected via primary query: rank.confidence=1.000, 3.35km from Chennai Central (within 40.0km validation threshold), geoapify place_id=510c67c8c221125440592f6013e3461b2a40f00102f90108765d0100000000c0020192030c4d6172696e61204265616368.</t>
         </is>
       </c>
     </row>
@@ -1066,15 +1154,58 @@
           <t>Fort St. George</t>
         </is>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Fort St. George, Chennai, Tamil Nadu, India</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Fort St. George, Rajaji Salai, Zone 5 Royapuram, Chennai - 600009, TN, India</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tamil Nadu</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
         <v>13.0798617</v>
       </c>
-      <c r="D3" t="n">
+      <c r="I3" t="n">
         <v>80.2846692</v>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>OSM Nominatim</t>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Geoapify Geocoding API</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>https://api.geoapify.com/v1/geocode/search?text=Fort St. George, Chennai, Tamil Nadu, India&amp;filter=circle:80.2763077,13.0825901,30000&amp;bias=proximity:80.2763077,13.0825901&amp;limit=5&amp;format=json</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>2026-09-14T04:15:20.230531+00:00</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Selected via primary query: rank.confidence=1.000, 0.96km from Chennai Central (within 40.0km validation threshold), geoapify place_id=516c0b2a053812544059eb67fba1e3282a40f00102f9016a00374600000000c0020192030f466f72742053742e2047656f726765.</t>
         </is>
       </c>
     </row>
@@ -1089,15 +1220,58 @@
           <t>Kapaleeshwarar Temple</t>
         </is>
       </c>
-      <c r="C4" t="n">
-        <v>13.0334336</v>
-      </c>
-      <c r="D4" t="n">
-        <v>80.26869600000001</v>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Kapaleeshwarar Temple, Chennai, Tamil Nadu, India</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Mylapore Kapaleeshwarar Temple Tank, East Tank Square Street, Zone 9 Teynampet, Chennai - 600004, TN, India</t>
+        </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>OSM Nominatim</t>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tamil Nadu</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>13.0334291</v>
+      </c>
+      <c r="I4" t="n">
+        <v>80.2686576</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Geoapify Geocoding API</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>https://api.geoapify.com/v1/geocode/search?text=Kapaleeshwarar Temple, Chennai, Tamil Nadu, India&amp;filter=circle:80.2763077,13.0825901,30000&amp;bias=proximity:80.2763077,13.0825901&amp;limit=5&amp;format=json</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>2026-09-14T04:15:21.788338+00:00</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Selected via primary query: rank.confidence=0.810, 5.53km from Chennai Central (within 40.0km validation threshold), geoapify place_id=519974a5af31115440592c78769e1d112a40f00102f901887d6e0c00000000c002019203234d796c61706f7265204b6170616c6565736877617261722054656d706c652054616e6b.</t>
         </is>
       </c>
     </row>
@@ -1112,15 +1286,58 @@
           <t>San Thome Basilica</t>
         </is>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>St Thomas Basilica, Chennai, India</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>St. Thomas Cathedral Basilica, 12, Rosary Church Road, Santhome, Chennai - 600004, TN, India</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tamil Nadu</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
         <v>13.0335889</v>
       </c>
-      <c r="D5" t="n">
+      <c r="I5" t="n">
         <v>80.2777851</v>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>OSM Nominatim</t>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Geoapify Geocoding API</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>https://api.geoapify.com/v1/geocode/search?text=St Thomas Basilica, Chennai, India&amp;filter=circle:80.2763077,13.0825901,30000&amp;bias=proximity:80.2763077,13.0825901&amp;limit=5&amp;format=json</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>2026-09-14T04:15:25.767302+00:00</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Selected via fallback query: rank.confidence=0.900, 5.45km from Chennai Central (within 40.0km validation threshold), geoapify place_id=513bf4273bc7115440596904769032112a40f00102f9017cb67b4200000000c0020192031d53742e2054686f6d61732043617468656472616c20426173696c696361.</t>
         </is>
       </c>
     </row>
@@ -1135,15 +1352,58 @@
           <t>Government Museum, Chennai</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Government Museum, Chennai, Chennai, Tamil Nadu, India</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Chennai Government Museum, பாந்தியன் சாலை, Zone 5 Royapuram, Chennai - 600008, TN, India</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tamil Nadu</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
         <v>13.0712808</v>
       </c>
-      <c r="D6" t="n">
+      <c r="I6" t="n">
         <v>80.25704330000001</v>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>OSM Nominatim</t>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Geoapify Geocoding API</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>https://api.geoapify.com/v1/geocode/search?text=Government Museum, Chennai, Chennai, Tamil Nadu, India&amp;filter=circle:80.2763077,13.0825901,30000&amp;bias=proximity:80.2763077,13.0825901&amp;limit=5&amp;format=json</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>2026-09-14T04:15:27.500956+00:00</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Selected via primary query: rank.confidence=0.900, 2.44km from Chennai Central (within 40.0km validation threshold), geoapify place_id=51fbc9bd6573105440595aaac1ea7e242a40f00102f901e1472c4300000000c002019203194368656e6e616920476f7665726e6d656e74204d757365756d.</t>
         </is>
       </c>
     </row>
@@ -1158,15 +1418,58 @@
           <t>Guindy National Park</t>
         </is>
       </c>
-      <c r="C7" t="n">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Guindy National Park, Chennai, Tamil Nadu, India</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Guindy National Park, Chennai, India</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tamil Nadu</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
         <v>13.000005</v>
       </c>
-      <c r="D7" t="n">
+      <c r="I7" t="n">
         <v>80.22804480000001</v>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>OSM Nominatim</t>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Geoapify Geocoding API</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>https://api.geoapify.com/v1/geocode/search?text=Guindy National Park, Chennai, Tamil Nadu, India&amp;filter=circle:80.2763077,13.0825901,30000&amp;bias=proximity:80.2763077,13.0825901&amp;limit=5&amp;format=json</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>2026-09-14T04:15:29.140545+00:00</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Selected via primary query: rank.confidence=1.000, 10.57km from Chennai Central (within 40.0km validation threshold), geoapify place_id=5177813749980e54405947acc5a700002a40f00102f901d4907d0100000000c002019203144775696e6479204e6174696f6e616c205061726b.</t>
         </is>
       </c>
     </row>
@@ -1181,15 +1484,58 @@
           <t>Arignar Anna Zoological Park (Vandalur Zoo)</t>
         </is>
       </c>
-      <c r="C8" t="n">
-        <v>12.8800708</v>
-      </c>
-      <c r="D8" t="n">
-        <v>80.08234539999999</v>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Arignar Anna Zoological Park, Vandalur, Chennai, Tamil Nadu, India</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Arignar Anna Zoo Park, Perungalathur Flyover Ramp, Vandalur - 600063, TN, India</t>
+        </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>OSM Nominatim</t>
+          <t>Vandalur</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tamil Nadu</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>12.8834325</v>
+      </c>
+      <c r="I8" t="n">
+        <v>80.0915303</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Geoapify Geocoding API</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>https://api.geoapify.com/v1/geocode/search?text=Arignar Anna Zoological Park, Vandalur, Chennai, Tamil Nadu, India&amp;filter=circle:80.2763077,13.0825901,30000&amp;bias=proximity:80.2763077,13.0825901&amp;limit=5&amp;format=json</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>2026-09-14T04:15:33.032758+00:00</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Selected via fallback query: rank.confidence=1.000, 29.85km from Chennai Central (within 40.0km validation threshold), geoapify place_id=51f545e7a1db055440597172bf4351c42940f00102f9014867ae0100000000c00201920315417269676e617220416e6e61205a6f6f205061726b.</t>
         </is>
       </c>
     </row>
@@ -1204,15 +1550,58 @@
           <t>Valluvar Kottam</t>
         </is>
       </c>
-      <c r="C9" t="n">
-        <v>13.0540763</v>
-      </c>
-      <c r="D9" t="n">
-        <v>80.2418275</v>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Valluvar Kottam, Chennai, Tamil Nadu, India</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Valluvar Kottam High Road, Zone 9 Teynampet, Chennai - 600034, TN, India</t>
+        </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>OSM Nominatim</t>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tamil Nadu</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>13.05383</v>
+      </c>
+      <c r="I9" t="n">
+        <v>80.2423007</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Geoapify Geocoding API</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>https://api.geoapify.com/v1/geocode/search?text=Valluvar Kottam, Chennai, Tamil Nadu, India&amp;filter=circle:80.2763077,13.0825901,30000&amp;bias=proximity:80.2763077,13.0825901&amp;limit=5&amp;format=json</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>2026-09-14T04:15:34.508015+00:00</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Selected via primary query: rank.confidence=0.900, 4.88km from Chennai Central (within 40.0km validation threshold), geoapify place_id=511193cbda810f5440595d16139b8f1b2a40f00103f901685333d501000000c0020192030f56616c6c75766172204b6f7474616d.</t>
         </is>
       </c>
     </row>
@@ -1227,15 +1616,58 @@
           <t>Birla Planetarium</t>
         </is>
       </c>
-      <c r="C10" t="n">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Birla Planetarium, Chennai, Tamil Nadu, India</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Birla Planetarium, Lake View Road, Zone 13 Adyar, Chennai - 600085, TN, India</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tamil Nadu</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
         <v>13.0119591</v>
       </c>
-      <c r="D10" t="n">
+      <c r="I10" t="n">
         <v>80.2440161</v>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>OSM Nominatim</t>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Geoapify Geocoding API</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>https://api.geoapify.com/v1/geocode/search?text=Birla Planetarium, Chennai, Tamil Nadu, India&amp;filter=circle:80.2763077,13.0825901,30000&amp;bias=proximity:80.2763077,13.0825901&amp;limit=5&amp;format=json</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>2026-09-14T04:15:36.206548+00:00</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Selected via primary query: rank.confidence=1.000, 8.60km from Chennai Central (within 40.0km validation threshold), geoapify place_id=51a34cb4f59d0f54405979c7ce801f062a40f00103f90134127b1800000000c002019203114269726c6120506c616e6574617269756d.</t>
         </is>
       </c>
     </row>
@@ -1250,15 +1682,58 @@
           <t>Semmozhi Poonga</t>
         </is>
       </c>
-      <c r="C11" t="n">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Semmozhi Poonga, Chennai, Tamil Nadu, India</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Semmozhi Poonga, Zone 9 Teynampet, Chennai - 600086, TN, India</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tamil Nadu</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
         <v>13.0506767</v>
       </c>
-      <c r="D11" t="n">
+      <c r="I11" t="n">
         <v>80.2514735</v>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>OSM Nominatim</t>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Geoapify Geocoding API</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>https://api.geoapify.com/v1/geocode/search?text=Semmozhi Poonga, Chennai, Tamil Nadu, India&amp;filter=circle:80.2763077,13.0825901,30000&amp;bias=proximity:80.2763077,13.0825901&amp;limit=5&amp;format=json</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>2026-09-14T04:15:37.950994+00:00</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Selected via primary query: rank.confidence=1.000, 4.45km from Chennai Central (within 40.0km validation threshold), geoapify place_id=51e2934e241810544059a256e24bf2192a40f00102f901edcd890100000000c0020192030f53656d6d6f7a686920506f6f6e6761.</t>
         </is>
       </c>
     </row>
@@ -1273,15 +1748,58 @@
           <t>Elliot's Beach</t>
         </is>
       </c>
-      <c r="C12" t="n">
-        <v>12.9969493</v>
-      </c>
-      <c r="D12" t="n">
-        <v>80.27087059999999</v>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Elliot's Beach, Chennai, Tamil Nadu, India</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Elliot's Beach Gym, Elliot's Beach Promenade, Zone 13 Adyar, Chennai - 600090, TN, India</t>
+        </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>OSM Nominatim</t>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tamil Nadu</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>13.0001673</v>
+      </c>
+      <c r="I12" t="n">
+        <v>80.2711805</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Geoapify Geocoding API</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>https://api.geoapify.com/v1/geocode/search?text=Elliot's Beach, Chennai, Tamil Nadu, India&amp;filter=circle:80.2763077,13.0825901,30000&amp;bias=proximity:80.2763077,13.0825901&amp;limit=5&amp;format=json</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>2026-09-14T04:15:39.859108+00:00</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Selected via primary query: rank.confidence=0.900, 9.18km from Chennai Central (within 40.0km validation threshold), geoapify place_id=5107b474055b11544059a70ea8ed15002a40f00102f901342c7b4300000000c00201920312456c6c696f7427732042656163682047796d.</t>
         </is>
       </c>
     </row>
@@ -1296,15 +1814,58 @@
           <t>Besant Nagar Beach</t>
         </is>
       </c>
-      <c r="C13" t="n">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Besant Nagar Beach, Chennai, Tamil Nadu, India</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Elliots Beach, Zone 13 Adyar, Chennai, India</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tamil Nadu</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
         <v>12.9978811</v>
       </c>
-      <c r="D13" t="n">
+      <c r="I13" t="n">
         <v>80.2718515</v>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>OSM Nominatim</t>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Geoapify Geocoding API</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>https://api.geoapify.com/v1/geocode/search?text=Besant Nagar Beach, Chennai, Tamil Nadu, India&amp;filter=circle:80.2763077,13.0825901,30000&amp;bias=proximity:80.2763077,13.0825901&amp;limit=5&amp;format=json</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>2026-09-14T04:15:41.528795+00:00</t>
+        </is>
+      </c>
+      <c r="M13" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Selected via primary query: rank.confidence=1.000, 9.43km from Chennai Central (within 40.0km validation threshold), geoapify place_id=519677d5036611544059d0978345eafe2940f00101f9018443da0000000000c0020192030d456c6c696f7473204265616368.</t>
         </is>
       </c>
     </row>
@@ -1319,15 +1880,34 @@
           <t>DakshinaChitra</t>
         </is>
       </c>
-      <c r="C14" t="n">
-        <v>12.822513</v>
-      </c>
-      <c r="D14" t="n">
-        <v>80.2435254</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>OSM Overpass (name-substring search; not indexed by Nominatim)</t>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>DakshinaChitra, Chennai, Tamil Nadu, India</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Geoapify Geocoding API</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>https://api.geoapify.com/v1/geocode/search?text=DakshinaChitra, Chennai, Tamil Nadu, India&amp;filter=circle:80.2763077,13.0825901,30000&amp;bias=proximity:80.2763077,13.0825901&amp;limit=5&amp;format=json</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>2026-09-14T04:15:43.473686+00:00</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>needs_manual_review</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>No Geoapify result within 40.0km of Chennai Central for 1 query tried ('DakshinaChitra, Chennai, Tamil Nadu, India'). Coordinates intentionally left blank rather than guessed; needs manual review.</t>
         </is>
       </c>
     </row>
@@ -1342,15 +1922,58 @@
           <t>Cholamandal Artists' Village</t>
         </is>
       </c>
-      <c r="C15" t="n">
-        <v>12.9224139</v>
-      </c>
-      <c r="D15" t="n">
-        <v>80.2522779</v>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Cholamandal Artists' Village, Chennai, Tamil Nadu, India</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Cholamandal Artists' Village, East Coast Road, Zone 15 Sholinganallur, Chennai - 600115, TN, India</t>
+        </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>OSM Nominatim</t>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tamil Nadu</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>12.9229059</v>
+      </c>
+      <c r="I15" t="n">
+        <v>80.25172809999999</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Geoapify Geocoding API</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>https://api.geoapify.com/v1/geocode/search?text=Cholamandal Artists' Village, Chennai, Tamil Nadu, India&amp;filter=circle:80.2763077,13.0825901,30000&amp;bias=proximity:80.2763077,13.0825901&amp;limit=5&amp;format=json</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>2026-09-14T04:15:45.227749+00:00</t>
+        </is>
+      </c>
+      <c r="M15" t="n">
+        <v>1</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Selected via primary query: rank.confidence=1.000, 17.95km from Chennai Central (within 40.0km validation threshold), geoapify place_id=51fd3e2d501c105440592692431f87d82940f00103f901a6499fea00000000c0020192031c43686f6c616d616e64616c2041727469737473272056696c6c616765.</t>
         </is>
       </c>
     </row>
@@ -1365,15 +1988,34 @@
           <t>Vivekananda House</t>
         </is>
       </c>
-      <c r="C16" t="n">
-        <v>13.0495712</v>
-      </c>
-      <c r="D16" t="n">
-        <v>80.2802712</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>OSM Nominatim</t>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Vivekanandar Illam, Chennai, India</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Geoapify Geocoding API</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>https://api.geoapify.com/v1/geocode/search?text=Vivekanandar Illam, Chennai, India&amp;filter=circle:80.2763077,13.0825901,30000&amp;bias=proximity:80.2763077,13.0825901&amp;limit=5&amp;format=json</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>2026-09-14T04:15:48.458871+00:00</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>needs_manual_review</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>No Geoapify result within 40.0km of Chennai Central for 2 queries tried ('Vivekananda House, Chennai, Tamil Nadu, India'; 'Vivekanandar Illam, Chennai, India'). Coordinates intentionally left blank rather than guessed; needs manual review.</t>
         </is>
       </c>
     </row>
@@ -1388,15 +2030,58 @@
           <t>Thousand Lights Mosque</t>
         </is>
       </c>
-      <c r="C17" t="n">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Thousand Lights Mosque, Chennai, Tamil Nadu, India</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Thousand Lights Mosque, Anna Salai (Mount Road), Zone 9 Teynampet, Chennai - 600086, TN, India</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tamil Nadu</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
         <v>13.0550988</v>
       </c>
-      <c r="D17" t="n">
+      <c r="I17" t="n">
         <v>80.255239</v>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>OSM Nominatim</t>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Geoapify Geocoding API</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>https://api.geoapify.com/v1/geocode/search?text=Thousand Lights Mosque, Chennai, Tamil Nadu, India&amp;filter=circle:80.2763077,13.0825901,30000&amp;bias=proximity:80.2763077,13.0825901&amp;limit=5&amp;format=json</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>2026-09-14T04:15:50.036275+00:00</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Selected via primary query: rank.confidence=1.000, 3.81km from Chennai Central (within 40.0km validation threshold), geoapify place_id=517b6af5d555105440590219f0e8351c2a40f00102f9017542f90c00000000c0020192031654686f7573616e64204c6967687473204d6f73717565.</t>
         </is>
       </c>
     </row>
@@ -1411,15 +2096,58 @@
           <t>Parthasarathy Temple</t>
         </is>
       </c>
-      <c r="C18" t="n">
-        <v>13.0538288</v>
-      </c>
-      <c r="D18" t="n">
-        <v>80.2778941</v>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Parthasarathy Temple, Chennai, Tamil Nadu, India</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Arulmigu Parthasarathy Swamy Temple, South Mada Street, Zone 9 Teynampet, Chennai - 600005, TN, India</t>
+        </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>OSM Nominatim</t>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tamil Nadu</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>13.0539465</v>
+      </c>
+      <c r="I18" t="n">
+        <v>80.2763547</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Geoapify Geocoding API</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>https://api.geoapify.com/v1/geocode/search?text=Parthasarathy Temple, Chennai, Tamil Nadu, India&amp;filter=circle:80.2763077,13.0825901,30000&amp;bias=proximity:80.2763077,13.0825901&amp;limit=5&amp;format=json</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>2026-09-14T04:15:51.849268+00:00</t>
+        </is>
+      </c>
+      <c r="M18" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Selected via primary query: rank.confidence=0.810, 3.19km from Chennai Central (within 40.0km validation threshold), geoapify place_id=5123a69fcbaf11544059a3772ae09e1b2a40f00101f90196cf530000000000c002019203234172756c6d6967752050617274686173617261746879205377616d792054656d706c65.</t>
         </is>
       </c>
     </row>
@@ -1434,15 +2162,58 @@
           <t>Vadapalani Murugan Temple</t>
         </is>
       </c>
-      <c r="C19" t="n">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Vadapalani Murugan Temple, Chennai, Tamil Nadu, India</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Vadapalani Murugan Temple Pond, Zone 10 Kodambakkam, Chennai, India</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tamil Nadu</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
         <v>13.0529847</v>
       </c>
-      <c r="D19" t="n">
+      <c r="I19" t="n">
         <v>80.21426409999999</v>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>OSM Nominatim</t>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Geoapify Geocoding API</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>https://api.geoapify.com/v1/geocode/search?text=Vadapalani Murugan Temple, Chennai, Tamil Nadu, India&amp;filter=circle:80.2763077,13.0825901,30000&amp;bias=proximity:80.2763077,13.0825901&amp;limit=5&amp;format=json</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>2026-09-14T04:15:53.525085+00:00</t>
+        </is>
+      </c>
+      <c r="M19" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Selected via primary query: rank.confidence=0.900, 7.48km from Chennai Central (within 40.0km validation threshold), geoapify place_id=513d8dc580b60d544059726083cf201b2a40f00102f90139c2a70100000000c0020192031e5661646170616c616e69204d75727567616e2054656d706c6520506f6e64.</t>
         </is>
       </c>
     </row>
@@ -1457,15 +2228,58 @@
           <t>Express Avenue</t>
         </is>
       </c>
-      <c r="C20" t="n">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Express Avenue, Chennai, Tamil Nadu, India</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Express Avenue Mall, Zone 9 Teynampet, Chennai - 600014, TN, India</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tamil Nadu</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
         <v>13.0588206</v>
       </c>
-      <c r="D20" t="n">
+      <c r="I20" t="n">
         <v>80.2641028</v>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>OSM Nominatim</t>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Geoapify Geocoding API</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>https://api.geoapify.com/v1/geocode/search?text=Express Avenue, Chennai, Tamil Nadu, India&amp;filter=circle:80.2763077,13.0825901,30000&amp;bias=proximity:80.2763077,13.0825901&amp;limit=5&amp;format=json</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>2026-09-14T04:15:55.045686+00:00</t>
+        </is>
+      </c>
+      <c r="M20" t="n">
+        <v>1</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Selected via primary query: rank.confidence=1.000, 2.96km from Chennai Central (within 40.0km validation threshold), geoapify place_id=510d326e0fe71054405986a9d2bb1d1e2a40f00102f901dbfff80c00000000c0020192031345787072657373204176656e7565204d616c6c.</t>
         </is>
       </c>
     </row>
@@ -1480,15 +2294,58 @@
           <t>MGM Dizzee World</t>
         </is>
       </c>
-      <c r="C21" t="n">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>MGM Dizzee World, Chennai, Tamil Nadu, India</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>MGM Dizzee World, 1/74, East Coast Road, Chennai - 600112, TN, India</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tamil Nadu</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
         <v>12.8258571</v>
       </c>
-      <c r="D21" t="n">
+      <c r="I21" t="n">
         <v>80.2452821</v>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>OSM Nominatim</t>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Geoapify Geocoding API</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>https://api.geoapify.com/v1/geocode/search?text=MGM Dizzee World, Chennai, Tamil Nadu, India&amp;filter=circle:80.2763077,13.0825901,30000&amp;bias=proximity:80.2763077,13.0825901&amp;limit=5&amp;format=json</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>2026-09-14T04:15:56.779222+00:00</t>
+        </is>
+      </c>
+      <c r="M21" t="n">
+        <v>1</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Selected via primary query: rank.confidence=1.000, 28.74km from Chennai Central (within 40.0km validation threshold), geoapify place_id=51d472b1b3b20f544059bc56e7bdd6a62940f00102f90198111d0200000000c002019203104d474d2044697a7a656520576f726c64.</t>
         </is>
       </c>
     </row>
@@ -19132,7 +19989,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G401"/>
+  <dimension ref="A1:G481"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33969,6 +34826,2966 @@
       <c r="G401" t="inlineStr">
         <is>
           <t>2026-09-10T09:31:25.019283+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>step02_coordinates</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>coordinates</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>Selected via primary query: rank.confidence=1.000, 3.35km from Chennai Central (within 40.0km validation threshold), geoapify place_id=510c67c8c221125440592f6013e3461b2a40f00102f90108765d0100000000c0020192030c4d6172696e61204265616368.</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>Geoapify Geocoding API</t>
+        </is>
+      </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>https://api.geoapify.com/v1/geocode/search?text=Marina Beach, Chennai, Tamil Nadu, India&amp;filter=circle:80.2763077,13.0825901,30000&amp;bias=proximity:80.2763077,13.0825901&amp;limit=5&amp;format=json</t>
+        </is>
+      </c>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>2026-09-14T04:05:30.833858+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>step02_coordinates</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>coordinates</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>Selected via primary query: rank.confidence=1.000, 0.96km from Chennai Central (within 40.0km validation threshold), geoapify place_id=516c0b2a053812544059eb67fba1e3282a40f00102f9016a00374600000000c0020192030f466f72742053742e2047656f726765.</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>Geoapify Geocoding API</t>
+        </is>
+      </c>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>https://api.geoapify.com/v1/geocode/search?text=Fort St. George, Chennai, Tamil Nadu, India&amp;filter=circle:80.2763077,13.0825901,30000&amp;bias=proximity:80.2763077,13.0825901&amp;limit=5&amp;format=json</t>
+        </is>
+      </c>
+      <c r="G403" t="inlineStr">
+        <is>
+          <t>2026-09-14T04:05:30.836850+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>step02_coordinates</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>P03</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>coordinates</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>Selected via primary query: rank.confidence=0.810, 5.53km from Chennai Central (within 40.0km validation threshold), geoapify place_id=519974a5af31115440592c78769e1d112a40f00102f901887d6e0c00000000c002019203234d796c61706f7265204b6170616c6565736877617261722054656d706c652054616e6b.</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>Geoapify Geocoding API</t>
+        </is>
+      </c>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>https://api.geoapify.com/v1/geocode/search?text=Kapaleeshwarar Temple, Chennai, Tamil Nadu, India&amp;filter=circle:80.2763077,13.0825901,30000&amp;bias=proximity:80.2763077,13.0825901&amp;limit=5&amp;format=json</t>
+        </is>
+      </c>
+      <c r="G404" t="inlineStr">
+        <is>
+          <t>2026-09-14T04:05:30.837858+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>step02_coordinates</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>P04</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>coordinates</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>Selected via primary query: rank.confidence=0.250, 0.67km from Chennai Central (within 40.0km validation threshold), geoapify place_id=51927538ba4a11544059d8bf46edd92a2a40f00101f901d6f31a0000000000c002089203074368656e6e6169.</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>Geoapify Geocoding API</t>
+        </is>
+      </c>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>https://api.geoapify.com/v1/geocode/search?text=San Thome Basilica, Chennai, Tamil Nadu, India&amp;filter=circle:80.2763077,13.0825901,30000&amp;bias=proximity:80.2763077,13.0825901&amp;limit=5&amp;format=json</t>
+        </is>
+      </c>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>2026-09-14T04:05:30.838861+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>step02_coordinates</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>coordinates</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>Selected via primary query: rank.confidence=0.900, 2.44km from Chennai Central (within 40.0km validation threshold), geoapify place_id=51fbc9bd6573105440595aaac1ea7e242a40f00102f901e1472c4300000000c002019203194368656e6e616920476f7665726e6d656e74204d757365756d.</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>Geoapify Geocoding API</t>
+        </is>
+      </c>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>https://api.geoapify.com/v1/geocode/search?text=Government Museum, Chennai, Chennai, Tamil Nadu, India&amp;filter=circle:80.2763077,13.0825901,30000&amp;bias=proximity:80.2763077,13.0825901&amp;limit=5&amp;format=json</t>
+        </is>
+      </c>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>2026-09-14T04:05:30.839851+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>step02_coordinates</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>P06</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>coordinates</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>Selected via primary query: rank.confidence=1.000, 10.57km from Chennai Central (within 40.0km validation threshold), geoapify place_id=5177813749980e54405947acc5a700002a40f00102f901d4907d0100000000c002019203144775696e6479204e6174696f6e616c205061726b.</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>Geoapify Geocoding API</t>
+        </is>
+      </c>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>https://api.geoapify.com/v1/geocode/search?text=Guindy National Park, Chennai, Tamil Nadu, India&amp;filter=circle:80.2763077,13.0825901,30000&amp;bias=proximity:80.2763077,13.0825901&amp;limit=5&amp;format=json</t>
+        </is>
+      </c>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>2026-09-14T04:05:30.840903+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>step02_coordinates</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>P07</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>coordinates</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>Selected via primary query: rank.confidence=0.250, 0.67km from Chennai Central (within 40.0km validation threshold), geoapify place_id=51927538ba4a11544059d8bf46edd92a2a40f00101f901d6f31a0000000000c002089203074368656e6e6169.</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>Geoapify Geocoding API</t>
+        </is>
+      </c>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>https://api.geoapify.com/v1/geocode/search?text=Arignar Anna Zoological Park (Vandalur Zoo), Chennai, Tamil Nadu, India&amp;filter=circle:80.2763077,13.0825901,30000&amp;bias=proximity:80.2763077,13.0825901&amp;limit=5&amp;format=json</t>
+        </is>
+      </c>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>2026-09-14T04:05:30.840903+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>step02_coordinates</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>P08</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>coordinates</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>Selected via primary query: rank.confidence=0.900, 4.88km from Chennai Central (within 40.0km validation threshold), geoapify place_id=511193cbda810f5440595d16139b8f1b2a40f00103f901685333d501000000c0020192030f56616c6c75766172204b6f7474616d.</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>Geoapify Geocoding API</t>
+        </is>
+      </c>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>https://api.geoapify.com/v1/geocode/search?text=Valluvar Kottam, Chennai, Tamil Nadu, India&amp;filter=circle:80.2763077,13.0825901,30000&amp;bias=proximity:80.2763077,13.0825901&amp;limit=5&amp;format=json</t>
+        </is>
+      </c>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>2026-09-14T04:05:30.841964+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>step02_coordinates</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>P09</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>coordinates</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>Selected via primary query: rank.confidence=1.000, 8.60km from Chennai Central (within 40.0km validation threshold), geoapify place_id=51a34cb4f59d0f54405979c7ce801f062a40f00103f90134127b1800000000c002019203114269726c6120506c616e6574617269756d.</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>Geoapify Geocoding API</t>
+        </is>
+      </c>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>https://api.geoapify.com/v1/geocode/search?text=Birla Planetarium, Chennai, Tamil Nadu, India&amp;filter=circle:80.2763077,13.0825901,30000&amp;bias=proximity:80.2763077,13.0825901&amp;limit=5&amp;format=json</t>
+        </is>
+      </c>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>2026-09-14T04:05:30.842864+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>step02_coordinates</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>coordinates</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>Selected via primary query: rank.confidence=1.000, 4.45km from Chennai Central (within 40.0km validation threshold), geoapify place_id=51e2934e241810544059a256e24bf2192a40f00102f901edcd890100000000c0020192030f53656d6d6f7a686920506f6f6e6761.</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>Geoapify Geocoding API</t>
+        </is>
+      </c>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>https://api.geoapify.com/v1/geocode/search?text=Semmozhi Poonga, Chennai, Tamil Nadu, India&amp;filter=circle:80.2763077,13.0825901,30000&amp;bias=proximity:80.2763077,13.0825901&amp;limit=5&amp;format=json</t>
+        </is>
+      </c>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>2026-09-14T04:05:30.843850+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>step02_coordinates</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>coordinates</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>Selected via primary query: rank.confidence=0.900, 9.18km from Chennai Central (within 40.0km validation threshold), geoapify place_id=5107b474055b11544059a70ea8ed15002a40f00102f901342c7b4300000000c00201920312456c6c696f7427732042656163682047796d.</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>Geoapify Geocoding API</t>
+        </is>
+      </c>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>https://api.geoapify.com/v1/geocode/search?text=Elliot's Beach, Chennai, Tamil Nadu, India&amp;filter=circle:80.2763077,13.0825901,30000&amp;bias=proximity:80.2763077,13.0825901&amp;limit=5&amp;format=json</t>
+        </is>
+      </c>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>2026-09-14T04:05:30.845854+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>step02_coordinates</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>P12</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>coordinates</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>Selected via primary query: rank.confidence=1.000, 9.43km from Chennai Central (within 40.0km validation threshold), geoapify place_id=519677d5036611544059d0978345eafe2940f00101f9018443da0000000000c0020192030d456c6c696f7473204265616368.</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>Geoapify Geocoding API</t>
+        </is>
+      </c>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>https://api.geoapify.com/v1/geocode/search?text=Besant Nagar Beach, Chennai, Tamil Nadu, India&amp;filter=circle:80.2763077,13.0825901,30000&amp;bias=proximity:80.2763077,13.0825901&amp;limit=5&amp;format=json</t>
+        </is>
+      </c>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>2026-09-14T04:05:30.846850+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>step02_coordinates</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>P13</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>coordinates</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>Selected via primary query: rank.confidence=0.250, 0.67km from Chennai Central (within 40.0km validation threshold), geoapify place_id=51927538ba4a11544059d8bf46edd92a2a40f00101f901d6f31a0000000000c002089203074368656e6e6169.</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>Geoapify Geocoding API</t>
+        </is>
+      </c>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>https://api.geoapify.com/v1/geocode/search?text=DakshinaChitra, Chennai, Tamil Nadu, India&amp;filter=circle:80.2763077,13.0825901,30000&amp;bias=proximity:80.2763077,13.0825901&amp;limit=5&amp;format=json</t>
+        </is>
+      </c>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>2026-09-14T04:05:30.847852+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>step02_coordinates</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>P14</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>coordinates</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>Selected via primary query: rank.confidence=1.000, 17.95km from Chennai Central (within 40.0km validation threshold), geoapify place_id=51fd3e2d501c105440592692431f87d82940f00103f901a6499fea00000000c0020192031c43686f6c616d616e64616c2041727469737473272056696c6c616765.</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>Geoapify Geocoding API</t>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>https://api.geoapify.com/v1/geocode/search?text=Cholamandal Artists' Village, Chennai, Tamil Nadu, India&amp;filter=circle:80.2763077,13.0825901,30000&amp;bias=proximity:80.2763077,13.0825901&amp;limit=5&amp;format=json</t>
+        </is>
+      </c>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>2026-09-14T04:05:30.848848+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>step02_coordinates</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>P15</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>coordinates</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>Selected via primary query: rank.confidence=1.000, 4.86km from Chennai Central (within 40.0km validation threshold), geoapify place_id=513a083a5ad5105440599f3bc1feeb142a40f00102f90134246d0100000000c00201e203206f70656e7374726565746d61703a76656e75653a7761792f3233393239393038.</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>Geoapify Geocoding API</t>
+        </is>
+      </c>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>https://api.geoapify.com/v1/geocode/search?text=Vivekananda House, Chennai, Tamil Nadu, India&amp;filter=circle:80.2763077,13.0825901,30000&amp;bias=proximity:80.2763077,13.0825901&amp;limit=5&amp;format=json</t>
+        </is>
+      </c>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>2026-09-14T04:05:30.849858+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>step02_coordinates</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>P16</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>coordinates</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>Selected via primary query: rank.confidence=1.000, 3.81km from Chennai Central (within 40.0km validation threshold), geoapify place_id=517b6af5d555105440590219f0e8351c2a40f00102f9017542f90c00000000c0020192031654686f7573616e64204c6967687473204d6f73717565.</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>Geoapify Geocoding API</t>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>https://api.geoapify.com/v1/geocode/search?text=Thousand Lights Mosque, Chennai, Tamil Nadu, India&amp;filter=circle:80.2763077,13.0825901,30000&amp;bias=proximity:80.2763077,13.0825901&amp;limit=5&amp;format=json</t>
+        </is>
+      </c>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>2026-09-14T04:05:30.850934+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>step02_coordinates</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>P17</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>coordinates</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>Selected via primary query: rank.confidence=0.810, 3.19km from Chennai Central (within 40.0km validation threshold), geoapify place_id=5123a69fcbaf11544059a3772ae09e1b2a40f00101f90196cf530000000000c002019203234172756c6d6967752050617274686173617261746879205377616d792054656d706c65.</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>Geoapify Geocoding API</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>https://api.geoapify.com/v1/geocode/search?text=Parthasarathy Temple, Chennai, Tamil Nadu, India&amp;filter=circle:80.2763077,13.0825901,30000&amp;bias=proximity:80.2763077,13.0825901&amp;limit=5&amp;format=json</t>
+        </is>
+      </c>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>2026-09-14T04:05:30.851957+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>step02_coordinates</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>P18</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>coordinates</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>Selected via primary query: rank.confidence=0.900, 7.48km from Chennai Central (within 40.0km validation threshold), geoapify place_id=513d8dc580b60d544059726083cf201b2a40f00102f90139c2a70100000000c0020192031e5661646170616c616e69204d75727567616e2054656d706c6520506f6e64.</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>Geoapify Geocoding API</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>https://api.geoapify.com/v1/geocode/search?text=Vadapalani Murugan Temple, Chennai, Tamil Nadu, India&amp;filter=circle:80.2763077,13.0825901,30000&amp;bias=proximity:80.2763077,13.0825901&amp;limit=5&amp;format=json</t>
+        </is>
+      </c>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>2026-09-14T04:05:30.852951+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>step02_coordinates</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>P19</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>coordinates</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>Selected via primary query: rank.confidence=1.000, 2.96km from Chennai Central (within 40.0km validation threshold), geoapify place_id=510d326e0fe71054405986a9d2bb1d1e2a40f00102f901dbfff80c00000000c0020192031345787072657373204176656e7565204d616c6c.</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>Geoapify Geocoding API</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>https://api.geoapify.com/v1/geocode/search?text=Express Avenue, Chennai, Tamil Nadu, India&amp;filter=circle:80.2763077,13.0825901,30000&amp;bias=proximity:80.2763077,13.0825901&amp;limit=5&amp;format=json</t>
+        </is>
+      </c>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>2026-09-14T04:05:30.854047+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>step02_coordinates</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>P20</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>coordinates</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>Selected via primary query: rank.confidence=1.000, 28.74km from Chennai Central (within 40.0km validation threshold), geoapify place_id=51d472b1b3b20f544059bc56e7bdd6a62940f00102f90198111d0200000000c002019203104d474d2044697a7a656520576f726c64.</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>Geoapify Geocoding API</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>https://api.geoapify.com/v1/geocode/search?text=MGM Dizzee World, Chennai, Tamil Nadu, India&amp;filter=circle:80.2763077,13.0825901,30000&amp;bias=proximity:80.2763077,13.0825901&amp;limit=5&amp;format=json</t>
+        </is>
+      </c>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>2026-09-14T04:05:30.854047+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>step02_coordinates</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>coordinates</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>Selected via primary query: rank.confidence=1.000, 3.35km from Chennai Central (within 40.0km validation threshold), geoapify place_id=510c67c8c221125440592f6013e3461b2a40f00102f90108765d0100000000c0020192030c4d6172696e61204265616368.</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>Geoapify Geocoding API</t>
+        </is>
+      </c>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>https://api.geoapify.com/v1/geocode/search?text=Marina Beach, Chennai, Tamil Nadu, India&amp;filter=circle:80.2763077,13.0825901,30000&amp;bias=proximity:80.2763077,13.0825901&amp;limit=5&amp;format=json</t>
+        </is>
+      </c>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>2026-09-14T04:10:54.204815+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>step02_coordinates</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>coordinates</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>Selected via primary query: rank.confidence=1.000, 0.96km from Chennai Central (within 40.0km validation threshold), geoapify place_id=516c0b2a053812544059eb67fba1e3282a40f00102f9016a00374600000000c0020192030f466f72742053742e2047656f726765.</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>Geoapify Geocoding API</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>https://api.geoapify.com/v1/geocode/search?text=Fort St. George, Chennai, Tamil Nadu, India&amp;filter=circle:80.2763077,13.0825901,30000&amp;bias=proximity:80.2763077,13.0825901&amp;limit=5&amp;format=json</t>
+        </is>
+      </c>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>2026-09-14T04:10:54.210493+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>step02_coordinates</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>P03</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>coordinates</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>Selected via primary query: rank.confidence=0.810, 5.53km from Chennai Central (within 40.0km validation threshold), geoapify place_id=519974a5af31115440592c78769e1d112a40f00102f901887d6e0c00000000c002019203234d796c61706f7265204b6170616c6565736877617261722054656d706c652054616e6b.</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>Geoapify Geocoding API</t>
+        </is>
+      </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>https://api.geoapify.com/v1/geocode/search?text=Kapaleeshwarar Temple, Chennai, Tamil Nadu, India&amp;filter=circle:80.2763077,13.0825901,30000&amp;bias=proximity:80.2763077,13.0825901&amp;limit=5&amp;format=json</t>
+        </is>
+      </c>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>2026-09-14T04:10:54.212604+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>step02_coordinates</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>P04</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>coordinates</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>Selected via fallback query: rank.confidence=0.900, 5.45km from Chennai Central (within 40.0km validation threshold), geoapify place_id=513bf4273bc7115440596904769032112a40f00102f9017cb67b4200000000c0020192031d53742e2054686f6d61732043617468656472616c20426173696c696361.</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>Geoapify Geocoding API</t>
+        </is>
+      </c>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>https://api.geoapify.com/v1/geocode/search?text=St Thomas Basilica, Chennai, India&amp;filter=circle:80.2763077,13.0825901,30000&amp;bias=proximity:80.2763077,13.0825901&amp;limit=5&amp;format=json</t>
+        </is>
+      </c>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>2026-09-14T04:10:54.214502+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>step02_coordinates</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>coordinates</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>Selected via primary query: rank.confidence=0.900, 2.44km from Chennai Central (within 40.0km validation threshold), geoapify place_id=51fbc9bd6573105440595aaac1ea7e242a40f00102f901e1472c4300000000c002019203194368656e6e616920476f7665726e6d656e74204d757365756d.</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>Geoapify Geocoding API</t>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>https://api.geoapify.com/v1/geocode/search?text=Government Museum, Chennai, Chennai, Tamil Nadu, India&amp;filter=circle:80.2763077,13.0825901,30000&amp;bias=proximity:80.2763077,13.0825901&amp;limit=5&amp;format=json</t>
+        </is>
+      </c>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>2026-09-14T04:10:54.215601+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>step02_coordinates</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>P06</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>coordinates</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>Selected via primary query: rank.confidence=1.000, 10.57km from Chennai Central (within 40.0km validation threshold), geoapify place_id=5177813749980e54405947acc5a700002a40f00102f901d4907d0100000000c002019203144775696e6479204e6174696f6e616c205061726b.</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>Geoapify Geocoding API</t>
+        </is>
+      </c>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>https://api.geoapify.com/v1/geocode/search?text=Guindy National Park, Chennai, Tamil Nadu, India&amp;filter=circle:80.2763077,13.0825901,30000&amp;bias=proximity:80.2763077,13.0825901&amp;limit=5&amp;format=json</t>
+        </is>
+      </c>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>2026-09-14T04:10:54.217176+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>step02_coordinates</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>P07</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>coordinates</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>Selected via fallback query: rank.confidence=1.000, 29.85km from Chennai Central (within 40.0km validation threshold), geoapify place_id=51f545e7a1db055440597172bf4351c42940f00102f9014867ae0100000000c00201920315417269676e617220416e6e61205a6f6f205061726b.</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>Geoapify Geocoding API</t>
+        </is>
+      </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>https://api.geoapify.com/v1/geocode/search?text=Arignar Anna Zoological Park, Vandalur, Chennai, Tamil Nadu, India&amp;filter=circle:80.2763077,13.0825901,30000&amp;bias=proximity:80.2763077,13.0825901&amp;limit=5&amp;format=json</t>
+        </is>
+      </c>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>2026-09-14T04:10:54.218207+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>step02_coordinates</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>P08</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>coordinates</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>Selected via primary query: rank.confidence=0.900, 4.88km from Chennai Central (within 40.0km validation threshold), geoapify place_id=511193cbda810f5440595d16139b8f1b2a40f00103f901685333d501000000c0020192030f56616c6c75766172204b6f7474616d.</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>Geoapify Geocoding API</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>https://api.geoapify.com/v1/geocode/search?text=Valluvar Kottam, Chennai, Tamil Nadu, India&amp;filter=circle:80.2763077,13.0825901,30000&amp;bias=proximity:80.2763077,13.0825901&amp;limit=5&amp;format=json</t>
+        </is>
+      </c>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>2026-09-14T04:10:54.220190+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>step02_coordinates</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>P09</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>coordinates</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>Selected via primary query: rank.confidence=1.000, 8.60km from Chennai Central (within 40.0km validation threshold), geoapify place_id=51a34cb4f59d0f54405979c7ce801f062a40f00103f90134127b1800000000c002019203114269726c6120506c616e6574617269756d.</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>Geoapify Geocoding API</t>
+        </is>
+      </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>https://api.geoapify.com/v1/geocode/search?text=Birla Planetarium, Chennai, Tamil Nadu, India&amp;filter=circle:80.2763077,13.0825901,30000&amp;bias=proximity:80.2763077,13.0825901&amp;limit=5&amp;format=json</t>
+        </is>
+      </c>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>2026-09-14T04:10:54.221192+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>step02_coordinates</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>coordinates</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>Selected via primary query: rank.confidence=1.000, 4.45km from Chennai Central (within 40.0km validation threshold), geoapify place_id=51e2934e241810544059a256e24bf2192a40f00102f901edcd890100000000c0020192030f53656d6d6f7a686920506f6f6e6761.</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>Geoapify Geocoding API</t>
+        </is>
+      </c>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>https://api.geoapify.com/v1/geocode/search?text=Semmozhi Poonga, Chennai, Tamil Nadu, India&amp;filter=circle:80.2763077,13.0825901,30000&amp;bias=proximity:80.2763077,13.0825901&amp;limit=5&amp;format=json</t>
+        </is>
+      </c>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>2026-09-14T04:10:54.223494+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>step02_coordinates</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>coordinates</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>Selected via primary query: rank.confidence=0.900, 9.18km from Chennai Central (within 40.0km validation threshold), geoapify place_id=5107b474055b11544059a70ea8ed15002a40f00102f901342c7b4300000000c00201920312456c6c696f7427732042656163682047796d.</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>Geoapify Geocoding API</t>
+        </is>
+      </c>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>https://api.geoapify.com/v1/geocode/search?text=Elliot's Beach, Chennai, Tamil Nadu, India&amp;filter=circle:80.2763077,13.0825901,30000&amp;bias=proximity:80.2763077,13.0825901&amp;limit=5&amp;format=json</t>
+        </is>
+      </c>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>2026-09-14T04:10:54.225564+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>step02_coordinates</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>P12</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>coordinates</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>Selected via primary query: rank.confidence=1.000, 9.43km from Chennai Central (within 40.0km validation threshold), geoapify place_id=519677d5036611544059d0978345eafe2940f00101f9018443da0000000000c0020192030d456c6c696f7473204265616368.</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>Geoapify Geocoding API</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>https://api.geoapify.com/v1/geocode/search?text=Besant Nagar Beach, Chennai, Tamil Nadu, India&amp;filter=circle:80.2763077,13.0825901,30000&amp;bias=proximity:80.2763077,13.0825901&amp;limit=5&amp;format=json</t>
+        </is>
+      </c>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>2026-09-14T04:10:54.227546+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>step02_coordinates</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>P13</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>coordinates</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>No Geoapify result within 40.0km of Chennai Central for 1 query tried ('DakshinaChitra, Chennai, Tamil Nadu, India'). Coordinates intentionally left blank rather than guessed; needs manual review.</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>Geoapify Geocoding API</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>https://api.geoapify.com/v1/geocode/search?text=DakshinaChitra, Chennai, Tamil Nadu, India&amp;filter=circle:80.2763077,13.0825901,30000&amp;bias=proximity:80.2763077,13.0825901&amp;limit=5&amp;format=json</t>
+        </is>
+      </c>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>2026-09-14T04:10:54.229107+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>step02_coordinates</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>P14</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>coordinates</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>Selected via primary query: rank.confidence=1.000, 17.95km from Chennai Central (within 40.0km validation threshold), geoapify place_id=51fd3e2d501c105440592692431f87d82940f00103f901a6499fea00000000c0020192031c43686f6c616d616e64616c2041727469737473272056696c6c616765.</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>Geoapify Geocoding API</t>
+        </is>
+      </c>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>https://api.geoapify.com/v1/geocode/search?text=Cholamandal Artists' Village, Chennai, Tamil Nadu, India&amp;filter=circle:80.2763077,13.0825901,30000&amp;bias=proximity:80.2763077,13.0825901&amp;limit=5&amp;format=json</t>
+        </is>
+      </c>
+      <c r="G435" t="inlineStr">
+        <is>
+          <t>2026-09-14T04:10:54.230089+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>step02_coordinates</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>P15</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>coordinates</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>Selected via primary query: rank.confidence=1.000, 4.86km from Chennai Central (within 40.0km validation threshold), geoapify place_id=513a083a5ad5105440599f3bc1feeb142a40f00102f90134246d0100000000c00201e203206f70656e7374726565746d61703a76656e75653a7761792f3233393239393038.</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>Geoapify Geocoding API</t>
+        </is>
+      </c>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t>https://api.geoapify.com/v1/geocode/search?text=Vivekananda House, Chennai, Tamil Nadu, India&amp;filter=circle:80.2763077,13.0825901,30000&amp;bias=proximity:80.2763077,13.0825901&amp;limit=5&amp;format=json</t>
+        </is>
+      </c>
+      <c r="G436" t="inlineStr">
+        <is>
+          <t>2026-09-14T04:10:54.231175+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>step02_coordinates</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>P16</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>coordinates</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>Selected via primary query: rank.confidence=1.000, 3.81km from Chennai Central (within 40.0km validation threshold), geoapify place_id=517b6af5d555105440590219f0e8351c2a40f00102f9017542f90c00000000c0020192031654686f7573616e64204c6967687473204d6f73717565.</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>Geoapify Geocoding API</t>
+        </is>
+      </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>https://api.geoapify.com/v1/geocode/search?text=Thousand Lights Mosque, Chennai, Tamil Nadu, India&amp;filter=circle:80.2763077,13.0825901,30000&amp;bias=proximity:80.2763077,13.0825901&amp;limit=5&amp;format=json</t>
+        </is>
+      </c>
+      <c r="G437" t="inlineStr">
+        <is>
+          <t>2026-09-14T04:10:54.232100+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>step02_coordinates</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>P17</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>coordinates</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>Selected via primary query: rank.confidence=0.810, 3.19km from Chennai Central (within 40.0km validation threshold), geoapify place_id=5123a69fcbaf11544059a3772ae09e1b2a40f00101f90196cf530000000000c002019203234172756c6d6967752050617274686173617261746879205377616d792054656d706c65.</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>Geoapify Geocoding API</t>
+        </is>
+      </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>https://api.geoapify.com/v1/geocode/search?text=Parthasarathy Temple, Chennai, Tamil Nadu, India&amp;filter=circle:80.2763077,13.0825901,30000&amp;bias=proximity:80.2763077,13.0825901&amp;limit=5&amp;format=json</t>
+        </is>
+      </c>
+      <c r="G438" t="inlineStr">
+        <is>
+          <t>2026-09-14T04:10:54.233105+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>step02_coordinates</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>P18</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>coordinates</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>Selected via primary query: rank.confidence=0.900, 7.48km from Chennai Central (within 40.0km validation threshold), geoapify place_id=513d8dc580b60d544059726083cf201b2a40f00102f90139c2a70100000000c0020192031e5661646170616c616e69204d75727567616e2054656d706c6520506f6e64.</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>Geoapify Geocoding API</t>
+        </is>
+      </c>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>https://api.geoapify.com/v1/geocode/search?text=Vadapalani Murugan Temple, Chennai, Tamil Nadu, India&amp;filter=circle:80.2763077,13.0825901,30000&amp;bias=proximity:80.2763077,13.0825901&amp;limit=5&amp;format=json</t>
+        </is>
+      </c>
+      <c r="G439" t="inlineStr">
+        <is>
+          <t>2026-09-14T04:10:54.235209+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>step02_coordinates</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>P19</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>coordinates</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>Selected via primary query: rank.confidence=1.000, 2.96km from Chennai Central (within 40.0km validation threshold), geoapify place_id=510d326e0fe71054405986a9d2bb1d1e2a40f00102f901dbfff80c00000000c0020192031345787072657373204176656e7565204d616c6c.</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>Geoapify Geocoding API</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>https://api.geoapify.com/v1/geocode/search?text=Express Avenue, Chennai, Tamil Nadu, India&amp;filter=circle:80.2763077,13.0825901,30000&amp;bias=proximity:80.2763077,13.0825901&amp;limit=5&amp;format=json</t>
+        </is>
+      </c>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>2026-09-14T04:10:54.236177+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>step02_coordinates</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>P20</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>coordinates</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>Selected via primary query: rank.confidence=1.000, 28.74km from Chennai Central (within 40.0km validation threshold), geoapify place_id=51d472b1b3b20f544059bc56e7bdd6a62940f00102f90198111d0200000000c002019203104d474d2044697a7a656520576f726c64.</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>Geoapify Geocoding API</t>
+        </is>
+      </c>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>https://api.geoapify.com/v1/geocode/search?text=MGM Dizzee World, Chennai, Tamil Nadu, India&amp;filter=circle:80.2763077,13.0825901,30000&amp;bias=proximity:80.2763077,13.0825901&amp;limit=5&amp;format=json</t>
+        </is>
+      </c>
+      <c r="G441" t="inlineStr">
+        <is>
+          <t>2026-09-14T04:10:54.238400+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>step02_coordinates</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>coordinates</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>Selected via primary query: rank.confidence=1.000, 3.35km from Chennai Central (within 40.0km validation threshold), geoapify place_id=510c67c8c221125440592f6013e3461b2a40f00102f90108765d0100000000c0020192030c4d6172696e61204265616368.</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>Geoapify Geocoding API</t>
+        </is>
+      </c>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>https://api.geoapify.com/v1/geocode/search?text=Marina Beach, Chennai, Tamil Nadu, India&amp;filter=circle:80.2763077,13.0825901,30000&amp;bias=proximity:80.2763077,13.0825901&amp;limit=5&amp;format=json</t>
+        </is>
+      </c>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>2026-09-14T04:14:43.868799+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>step02_coordinates</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>coordinates</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>Selected via primary query: rank.confidence=1.000, 0.96km from Chennai Central (within 40.0km validation threshold), geoapify place_id=516c0b2a053812544059eb67fba1e3282a40f00102f9016a00374600000000c0020192030f466f72742053742e2047656f726765.</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>Geoapify Geocoding API</t>
+        </is>
+      </c>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>https://api.geoapify.com/v1/geocode/search?text=Fort St. George, Chennai, Tamil Nadu, India&amp;filter=circle:80.2763077,13.0825901,30000&amp;bias=proximity:80.2763077,13.0825901&amp;limit=5&amp;format=json</t>
+        </is>
+      </c>
+      <c r="G443" t="inlineStr">
+        <is>
+          <t>2026-09-14T04:14:43.874797+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>step02_coordinates</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>P03</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>coordinates</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>Selected via primary query: rank.confidence=0.810, 5.53km from Chennai Central (within 40.0km validation threshold), geoapify place_id=519974a5af31115440592c78769e1d112a40f00102f901887d6e0c00000000c002019203234d796c61706f7265204b6170616c6565736877617261722054656d706c652054616e6b.</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>Geoapify Geocoding API</t>
+        </is>
+      </c>
+      <c r="F444" t="inlineStr">
+        <is>
+          <t>https://api.geoapify.com/v1/geocode/search?text=Kapaleeshwarar Temple, Chennai, Tamil Nadu, India&amp;filter=circle:80.2763077,13.0825901,30000&amp;bias=proximity:80.2763077,13.0825901&amp;limit=5&amp;format=json</t>
+        </is>
+      </c>
+      <c r="G444" t="inlineStr">
+        <is>
+          <t>2026-09-14T04:14:43.876796+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>step02_coordinates</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>P04</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>coordinates</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>Selected via fallback query: rank.confidence=0.900, 5.45km from Chennai Central (within 40.0km validation threshold), geoapify place_id=513bf4273bc7115440596904769032112a40f00102f9017cb67b4200000000c0020192031d53742e2054686f6d61732043617468656472616c20426173696c696361.</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>Geoapify Geocoding API</t>
+        </is>
+      </c>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>https://api.geoapify.com/v1/geocode/search?text=St Thomas Basilica, Chennai, India&amp;filter=circle:80.2763077,13.0825901,30000&amp;bias=proximity:80.2763077,13.0825901&amp;limit=5&amp;format=json</t>
+        </is>
+      </c>
+      <c r="G445" t="inlineStr">
+        <is>
+          <t>2026-09-14T04:14:43.877796+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>step02_coordinates</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>coordinates</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>Selected via primary query: rank.confidence=0.900, 2.44km from Chennai Central (within 40.0km validation threshold), geoapify place_id=51fbc9bd6573105440595aaac1ea7e242a40f00102f901e1472c4300000000c002019203194368656e6e616920476f7665726e6d656e74204d757365756d.</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>Geoapify Geocoding API</t>
+        </is>
+      </c>
+      <c r="F446" t="inlineStr">
+        <is>
+          <t>https://api.geoapify.com/v1/geocode/search?text=Government Museum, Chennai, Chennai, Tamil Nadu, India&amp;filter=circle:80.2763077,13.0825901,30000&amp;bias=proximity:80.2763077,13.0825901&amp;limit=5&amp;format=json</t>
+        </is>
+      </c>
+      <c r="G446" t="inlineStr">
+        <is>
+          <t>2026-09-14T04:14:43.879917+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>step02_coordinates</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>P06</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>coordinates</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>Selected via primary query: rank.confidence=1.000, 10.57km from Chennai Central (within 40.0km validation threshold), geoapify place_id=5177813749980e54405947acc5a700002a40f00102f901d4907d0100000000c002019203144775696e6479204e6174696f6e616c205061726b.</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>Geoapify Geocoding API</t>
+        </is>
+      </c>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>https://api.geoapify.com/v1/geocode/search?text=Guindy National Park, Chennai, Tamil Nadu, India&amp;filter=circle:80.2763077,13.0825901,30000&amp;bias=proximity:80.2763077,13.0825901&amp;limit=5&amp;format=json</t>
+        </is>
+      </c>
+      <c r="G447" t="inlineStr">
+        <is>
+          <t>2026-09-14T04:14:43.880909+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>step02_coordinates</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>P07</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>coordinates</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>Selected via fallback query: rank.confidence=1.000, 29.85km from Chennai Central (within 40.0km validation threshold), geoapify place_id=51f545e7a1db055440597172bf4351c42940f00102f9014867ae0100000000c00201920315417269676e617220416e6e61205a6f6f205061726b.</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>Geoapify Geocoding API</t>
+        </is>
+      </c>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t>https://api.geoapify.com/v1/geocode/search?text=Arignar Anna Zoological Park, Vandalur, Chennai, Tamil Nadu, India&amp;filter=circle:80.2763077,13.0825901,30000&amp;bias=proximity:80.2763077,13.0825901&amp;limit=5&amp;format=json</t>
+        </is>
+      </c>
+      <c r="G448" t="inlineStr">
+        <is>
+          <t>2026-09-14T04:14:43.881913+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>step02_coordinates</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>P08</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>coordinates</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>Selected via primary query: rank.confidence=0.900, 4.88km from Chennai Central (within 40.0km validation threshold), geoapify place_id=511193cbda810f5440595d16139b8f1b2a40f00103f901685333d501000000c0020192030f56616c6c75766172204b6f7474616d.</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>Geoapify Geocoding API</t>
+        </is>
+      </c>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t>https://api.geoapify.com/v1/geocode/search?text=Valluvar Kottam, Chennai, Tamil Nadu, India&amp;filter=circle:80.2763077,13.0825901,30000&amp;bias=proximity:80.2763077,13.0825901&amp;limit=5&amp;format=json</t>
+        </is>
+      </c>
+      <c r="G449" t="inlineStr">
+        <is>
+          <t>2026-09-14T04:14:43.882914+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>step02_coordinates</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>P09</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>coordinates</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>Selected via primary query: rank.confidence=1.000, 8.60km from Chennai Central (within 40.0km validation threshold), geoapify place_id=51a34cb4f59d0f54405979c7ce801f062a40f00103f90134127b1800000000c002019203114269726c6120506c616e6574617269756d.</t>
+        </is>
+      </c>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>Geoapify Geocoding API</t>
+        </is>
+      </c>
+      <c r="F450" t="inlineStr">
+        <is>
+          <t>https://api.geoapify.com/v1/geocode/search?text=Birla Planetarium, Chennai, Tamil Nadu, India&amp;filter=circle:80.2763077,13.0825901,30000&amp;bias=proximity:80.2763077,13.0825901&amp;limit=5&amp;format=json</t>
+        </is>
+      </c>
+      <c r="G450" t="inlineStr">
+        <is>
+          <t>2026-09-14T04:14:43.884913+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>step02_coordinates</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>coordinates</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>Selected via primary query: rank.confidence=1.000, 4.45km from Chennai Central (within 40.0km validation threshold), geoapify place_id=51e2934e241810544059a256e24bf2192a40f00102f901edcd890100000000c0020192030f53656d6d6f7a686920506f6f6e6761.</t>
+        </is>
+      </c>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>Geoapify Geocoding API</t>
+        </is>
+      </c>
+      <c r="F451" t="inlineStr">
+        <is>
+          <t>https://api.geoapify.com/v1/geocode/search?text=Semmozhi Poonga, Chennai, Tamil Nadu, India&amp;filter=circle:80.2763077,13.0825901,30000&amp;bias=proximity:80.2763077,13.0825901&amp;limit=5&amp;format=json</t>
+        </is>
+      </c>
+      <c r="G451" t="inlineStr">
+        <is>
+          <t>2026-09-14T04:14:43.885902+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>step02_coordinates</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>coordinates</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>Selected via primary query: rank.confidence=0.900, 9.18km from Chennai Central (within 40.0km validation threshold), geoapify place_id=5107b474055b11544059a70ea8ed15002a40f00102f901342c7b4300000000c00201920312456c6c696f7427732042656163682047796d.</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>Geoapify Geocoding API</t>
+        </is>
+      </c>
+      <c r="F452" t="inlineStr">
+        <is>
+          <t>https://api.geoapify.com/v1/geocode/search?text=Elliot's Beach, Chennai, Tamil Nadu, India&amp;filter=circle:80.2763077,13.0825901,30000&amp;bias=proximity:80.2763077,13.0825901&amp;limit=5&amp;format=json</t>
+        </is>
+      </c>
+      <c r="G452" t="inlineStr">
+        <is>
+          <t>2026-09-14T04:14:43.886906+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>step02_coordinates</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>P12</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>coordinates</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>Selected via primary query: rank.confidence=1.000, 9.43km from Chennai Central (within 40.0km validation threshold), geoapify place_id=519677d5036611544059d0978345eafe2940f00101f9018443da0000000000c0020192030d456c6c696f7473204265616368.</t>
+        </is>
+      </c>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>Geoapify Geocoding API</t>
+        </is>
+      </c>
+      <c r="F453" t="inlineStr">
+        <is>
+          <t>https://api.geoapify.com/v1/geocode/search?text=Besant Nagar Beach, Chennai, Tamil Nadu, India&amp;filter=circle:80.2763077,13.0825901,30000&amp;bias=proximity:80.2763077,13.0825901&amp;limit=5&amp;format=json</t>
+        </is>
+      </c>
+      <c r="G453" t="inlineStr">
+        <is>
+          <t>2026-09-14T04:14:43.887914+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>step02_coordinates</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>P13</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>coordinates</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>No Geoapify result within 40.0km of Chennai Central for 1 query tried ('DakshinaChitra, Chennai, Tamil Nadu, India'). Coordinates intentionally left blank rather than guessed; needs manual review.</t>
+        </is>
+      </c>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>Geoapify Geocoding API</t>
+        </is>
+      </c>
+      <c r="F454" t="inlineStr">
+        <is>
+          <t>https://api.geoapify.com/v1/geocode/search?text=DakshinaChitra, Chennai, Tamil Nadu, India&amp;filter=circle:80.2763077,13.0825901,30000&amp;bias=proximity:80.2763077,13.0825901&amp;limit=5&amp;format=json</t>
+        </is>
+      </c>
+      <c r="G454" t="inlineStr">
+        <is>
+          <t>2026-09-14T04:14:43.888801+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>step02_coordinates</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>P14</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>coordinates</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>Selected via primary query: rank.confidence=1.000, 17.95km from Chennai Central (within 40.0km validation threshold), geoapify place_id=51fd3e2d501c105440592692431f87d82940f00103f901a6499fea00000000c0020192031c43686f6c616d616e64616c2041727469737473272056696c6c616765.</t>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>Geoapify Geocoding API</t>
+        </is>
+      </c>
+      <c r="F455" t="inlineStr">
+        <is>
+          <t>https://api.geoapify.com/v1/geocode/search?text=Cholamandal Artists' Village, Chennai, Tamil Nadu, India&amp;filter=circle:80.2763077,13.0825901,30000&amp;bias=proximity:80.2763077,13.0825901&amp;limit=5&amp;format=json</t>
+        </is>
+      </c>
+      <c r="G455" t="inlineStr">
+        <is>
+          <t>2026-09-14T04:14:43.889811+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>step02_coordinates</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>P15</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>coordinates</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>No Geoapify result within 40.0km of Chennai Central for 2 queries tried ('Vivekananda House, Chennai, Tamil Nadu, India, Vivekanandar Illam, Chennai, India'). Coordinates intentionally left blank rather than guessed; needs manual review.</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>Geoapify Geocoding API</t>
+        </is>
+      </c>
+      <c r="F456" t="inlineStr">
+        <is>
+          <t>https://api.geoapify.com/v1/geocode/search?text=Vivekanandar Illam, Chennai, India&amp;filter=circle:80.2763077,13.0825901,30000&amp;bias=proximity:80.2763077,13.0825901&amp;limit=5&amp;format=json</t>
+        </is>
+      </c>
+      <c r="G456" t="inlineStr">
+        <is>
+          <t>2026-09-14T04:14:43.890802+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>step02_coordinates</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>P16</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>coordinates</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>Selected via primary query: rank.confidence=1.000, 3.81km from Chennai Central (within 40.0km validation threshold), geoapify place_id=517b6af5d555105440590219f0e8351c2a40f00102f9017542f90c00000000c0020192031654686f7573616e64204c6967687473204d6f73717565.</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>Geoapify Geocoding API</t>
+        </is>
+      </c>
+      <c r="F457" t="inlineStr">
+        <is>
+          <t>https://api.geoapify.com/v1/geocode/search?text=Thousand Lights Mosque, Chennai, Tamil Nadu, India&amp;filter=circle:80.2763077,13.0825901,30000&amp;bias=proximity:80.2763077,13.0825901&amp;limit=5&amp;format=json</t>
+        </is>
+      </c>
+      <c r="G457" t="inlineStr">
+        <is>
+          <t>2026-09-14T04:14:43.892803+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>step02_coordinates</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>P17</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>coordinates</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>Selected via primary query: rank.confidence=0.810, 3.19km from Chennai Central (within 40.0km validation threshold), geoapify place_id=5123a69fcbaf11544059a3772ae09e1b2a40f00101f90196cf530000000000c002019203234172756c6d6967752050617274686173617261746879205377616d792054656d706c65.</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>Geoapify Geocoding API</t>
+        </is>
+      </c>
+      <c r="F458" t="inlineStr">
+        <is>
+          <t>https://api.geoapify.com/v1/geocode/search?text=Parthasarathy Temple, Chennai, Tamil Nadu, India&amp;filter=circle:80.2763077,13.0825901,30000&amp;bias=proximity:80.2763077,13.0825901&amp;limit=5&amp;format=json</t>
+        </is>
+      </c>
+      <c r="G458" t="inlineStr">
+        <is>
+          <t>2026-09-14T04:14:43.892803+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>step02_coordinates</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>P18</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>coordinates</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>Selected via primary query: rank.confidence=0.900, 7.48km from Chennai Central (within 40.0km validation threshold), geoapify place_id=513d8dc580b60d544059726083cf201b2a40f00102f90139c2a70100000000c0020192031e5661646170616c616e69204d75727567616e2054656d706c6520506f6e64.</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>Geoapify Geocoding API</t>
+        </is>
+      </c>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>https://api.geoapify.com/v1/geocode/search?text=Vadapalani Murugan Temple, Chennai, Tamil Nadu, India&amp;filter=circle:80.2763077,13.0825901,30000&amp;bias=proximity:80.2763077,13.0825901&amp;limit=5&amp;format=json</t>
+        </is>
+      </c>
+      <c r="G459" t="inlineStr">
+        <is>
+          <t>2026-09-14T04:14:43.893902+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>step02_coordinates</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>P19</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>coordinates</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>Selected via primary query: rank.confidence=1.000, 2.96km from Chennai Central (within 40.0km validation threshold), geoapify place_id=510d326e0fe71054405986a9d2bb1d1e2a40f00102f901dbfff80c00000000c0020192031345787072657373204176656e7565204d616c6c.</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>Geoapify Geocoding API</t>
+        </is>
+      </c>
+      <c r="F460" t="inlineStr">
+        <is>
+          <t>https://api.geoapify.com/v1/geocode/search?text=Express Avenue, Chennai, Tamil Nadu, India&amp;filter=circle:80.2763077,13.0825901,30000&amp;bias=proximity:80.2763077,13.0825901&amp;limit=5&amp;format=json</t>
+        </is>
+      </c>
+      <c r="G460" t="inlineStr">
+        <is>
+          <t>2026-09-14T04:14:43.894846+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>step02_coordinates</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>P20</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>coordinates</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>Selected via primary query: rank.confidence=1.000, 28.74km from Chennai Central (within 40.0km validation threshold), geoapify place_id=51d472b1b3b20f544059bc56e7bdd6a62940f00102f90198111d0200000000c002019203104d474d2044697a7a656520576f726c64.</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>Geoapify Geocoding API</t>
+        </is>
+      </c>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>https://api.geoapify.com/v1/geocode/search?text=MGM Dizzee World, Chennai, Tamil Nadu, India&amp;filter=circle:80.2763077,13.0825901,30000&amp;bias=proximity:80.2763077,13.0825901&amp;limit=5&amp;format=json</t>
+        </is>
+      </c>
+      <c r="G461" t="inlineStr">
+        <is>
+          <t>2026-09-14T04:14:43.895866+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>step02_coordinates</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>coordinates</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>Selected via primary query: rank.confidence=1.000, 3.35km from Chennai Central (within 40.0km validation threshold), geoapify place_id=510c67c8c221125440592f6013e3461b2a40f00102f90108765d0100000000c0020192030c4d6172696e61204265616368.</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>Geoapify Geocoding API</t>
+        </is>
+      </c>
+      <c r="F462" t="inlineStr">
+        <is>
+          <t>https://api.geoapify.com/v1/geocode/search?text=Marina Beach, Chennai, Tamil Nadu, India&amp;filter=circle:80.2763077,13.0825901,30000&amp;bias=proximity:80.2763077,13.0825901&amp;limit=5&amp;format=json</t>
+        </is>
+      </c>
+      <c r="G462" t="inlineStr">
+        <is>
+          <t>2026-09-14T04:15:56.786319+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>step02_coordinates</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>coordinates</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>Selected via primary query: rank.confidence=1.000, 0.96km from Chennai Central (within 40.0km validation threshold), geoapify place_id=516c0b2a053812544059eb67fba1e3282a40f00102f9016a00374600000000c0020192030f466f72742053742e2047656f726765.</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>Geoapify Geocoding API</t>
+        </is>
+      </c>
+      <c r="F463" t="inlineStr">
+        <is>
+          <t>https://api.geoapify.com/v1/geocode/search?text=Fort St. George, Chennai, Tamil Nadu, India&amp;filter=circle:80.2763077,13.0825901,30000&amp;bias=proximity:80.2763077,13.0825901&amp;limit=5&amp;format=json</t>
+        </is>
+      </c>
+      <c r="G463" t="inlineStr">
+        <is>
+          <t>2026-09-14T04:15:56.787337+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>step02_coordinates</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>P03</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>coordinates</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>Selected via primary query: rank.confidence=0.810, 5.53km from Chennai Central (within 40.0km validation threshold), geoapify place_id=519974a5af31115440592c78769e1d112a40f00102f901887d6e0c00000000c002019203234d796c61706f7265204b6170616c6565736877617261722054656d706c652054616e6b.</t>
+        </is>
+      </c>
+      <c r="E464" t="inlineStr">
+        <is>
+          <t>Geoapify Geocoding API</t>
+        </is>
+      </c>
+      <c r="F464" t="inlineStr">
+        <is>
+          <t>https://api.geoapify.com/v1/geocode/search?text=Kapaleeshwarar Temple, Chennai, Tamil Nadu, India&amp;filter=circle:80.2763077,13.0825901,30000&amp;bias=proximity:80.2763077,13.0825901&amp;limit=5&amp;format=json</t>
+        </is>
+      </c>
+      <c r="G464" t="inlineStr">
+        <is>
+          <t>2026-09-14T04:15:56.788323+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>step02_coordinates</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>P04</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>coordinates</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>Selected via fallback query: rank.confidence=0.900, 5.45km from Chennai Central (within 40.0km validation threshold), geoapify place_id=513bf4273bc7115440596904769032112a40f00102f9017cb67b4200000000c0020192031d53742e2054686f6d61732043617468656472616c20426173696c696361.</t>
+        </is>
+      </c>
+      <c r="E465" t="inlineStr">
+        <is>
+          <t>Geoapify Geocoding API</t>
+        </is>
+      </c>
+      <c r="F465" t="inlineStr">
+        <is>
+          <t>https://api.geoapify.com/v1/geocode/search?text=St Thomas Basilica, Chennai, India&amp;filter=circle:80.2763077,13.0825901,30000&amp;bias=proximity:80.2763077,13.0825901&amp;limit=5&amp;format=json</t>
+        </is>
+      </c>
+      <c r="G465" t="inlineStr">
+        <is>
+          <t>2026-09-14T04:15:56.790727+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>step02_coordinates</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>coordinates</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>Selected via primary query: rank.confidence=0.900, 2.44km from Chennai Central (within 40.0km validation threshold), geoapify place_id=51fbc9bd6573105440595aaac1ea7e242a40f00102f901e1472c4300000000c002019203194368656e6e616920476f7665726e6d656e74204d757365756d.</t>
+        </is>
+      </c>
+      <c r="E466" t="inlineStr">
+        <is>
+          <t>Geoapify Geocoding API</t>
+        </is>
+      </c>
+      <c r="F466" t="inlineStr">
+        <is>
+          <t>https://api.geoapify.com/v1/geocode/search?text=Government Museum, Chennai, Chennai, Tamil Nadu, India&amp;filter=circle:80.2763077,13.0825901,30000&amp;bias=proximity:80.2763077,13.0825901&amp;limit=5&amp;format=json</t>
+        </is>
+      </c>
+      <c r="G466" t="inlineStr">
+        <is>
+          <t>2026-09-14T04:15:56.791384+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>step02_coordinates</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>P06</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>coordinates</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>Selected via primary query: rank.confidence=1.000, 10.57km from Chennai Central (within 40.0km validation threshold), geoapify place_id=5177813749980e54405947acc5a700002a40f00102f901d4907d0100000000c002019203144775696e6479204e6174696f6e616c205061726b.</t>
+        </is>
+      </c>
+      <c r="E467" t="inlineStr">
+        <is>
+          <t>Geoapify Geocoding API</t>
+        </is>
+      </c>
+      <c r="F467" t="inlineStr">
+        <is>
+          <t>https://api.geoapify.com/v1/geocode/search?text=Guindy National Park, Chennai, Tamil Nadu, India&amp;filter=circle:80.2763077,13.0825901,30000&amp;bias=proximity:80.2763077,13.0825901&amp;limit=5&amp;format=json</t>
+        </is>
+      </c>
+      <c r="G467" t="inlineStr">
+        <is>
+          <t>2026-09-14T04:15:56.792324+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>step02_coordinates</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>P07</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>coordinates</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>Selected via fallback query: rank.confidence=1.000, 29.85km from Chennai Central (within 40.0km validation threshold), geoapify place_id=51f545e7a1db055440597172bf4351c42940f00102f9014867ae0100000000c00201920315417269676e617220416e6e61205a6f6f205061726b.</t>
+        </is>
+      </c>
+      <c r="E468" t="inlineStr">
+        <is>
+          <t>Geoapify Geocoding API</t>
+        </is>
+      </c>
+      <c r="F468" t="inlineStr">
+        <is>
+          <t>https://api.geoapify.com/v1/geocode/search?text=Arignar Anna Zoological Park, Vandalur, Chennai, Tamil Nadu, India&amp;filter=circle:80.2763077,13.0825901,30000&amp;bias=proximity:80.2763077,13.0825901&amp;limit=5&amp;format=json</t>
+        </is>
+      </c>
+      <c r="G468" t="inlineStr">
+        <is>
+          <t>2026-09-14T04:15:56.793325+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>step02_coordinates</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>P08</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>coordinates</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>Selected via primary query: rank.confidence=0.900, 4.88km from Chennai Central (within 40.0km validation threshold), geoapify place_id=511193cbda810f5440595d16139b8f1b2a40f00103f901685333d501000000c0020192030f56616c6c75766172204b6f7474616d.</t>
+        </is>
+      </c>
+      <c r="E469" t="inlineStr">
+        <is>
+          <t>Geoapify Geocoding API</t>
+        </is>
+      </c>
+      <c r="F469" t="inlineStr">
+        <is>
+          <t>https://api.geoapify.com/v1/geocode/search?text=Valluvar Kottam, Chennai, Tamil Nadu, India&amp;filter=circle:80.2763077,13.0825901,30000&amp;bias=proximity:80.2763077,13.0825901&amp;limit=5&amp;format=json</t>
+        </is>
+      </c>
+      <c r="G469" t="inlineStr">
+        <is>
+          <t>2026-09-14T04:15:56.794322+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>step02_coordinates</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>P09</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>coordinates</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>Selected via primary query: rank.confidence=1.000, 8.60km from Chennai Central (within 40.0km validation threshold), geoapify place_id=51a34cb4f59d0f54405979c7ce801f062a40f00103f90134127b1800000000c002019203114269726c6120506c616e6574617269756d.</t>
+        </is>
+      </c>
+      <c r="E470" t="inlineStr">
+        <is>
+          <t>Geoapify Geocoding API</t>
+        </is>
+      </c>
+      <c r="F470" t="inlineStr">
+        <is>
+          <t>https://api.geoapify.com/v1/geocode/search?text=Birla Planetarium, Chennai, Tamil Nadu, India&amp;filter=circle:80.2763077,13.0825901,30000&amp;bias=proximity:80.2763077,13.0825901&amp;limit=5&amp;format=json</t>
+        </is>
+      </c>
+      <c r="G470" t="inlineStr">
+        <is>
+          <t>2026-09-14T04:15:56.795326+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>step02_coordinates</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>coordinates</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>Selected via primary query: rank.confidence=1.000, 4.45km from Chennai Central (within 40.0km validation threshold), geoapify place_id=51e2934e241810544059a256e24bf2192a40f00102f901edcd890100000000c0020192030f53656d6d6f7a686920506f6f6e6761.</t>
+        </is>
+      </c>
+      <c r="E471" t="inlineStr">
+        <is>
+          <t>Geoapify Geocoding API</t>
+        </is>
+      </c>
+      <c r="F471" t="inlineStr">
+        <is>
+          <t>https://api.geoapify.com/v1/geocode/search?text=Semmozhi Poonga, Chennai, Tamil Nadu, India&amp;filter=circle:80.2763077,13.0825901,30000&amp;bias=proximity:80.2763077,13.0825901&amp;limit=5&amp;format=json</t>
+        </is>
+      </c>
+      <c r="G471" t="inlineStr">
+        <is>
+          <t>2026-09-14T04:15:56.797328+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>step02_coordinates</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>coordinates</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>Selected via primary query: rank.confidence=0.900, 9.18km from Chennai Central (within 40.0km validation threshold), geoapify place_id=5107b474055b11544059a70ea8ed15002a40f00102f901342c7b4300000000c00201920312456c6c696f7427732042656163682047796d.</t>
+        </is>
+      </c>
+      <c r="E472" t="inlineStr">
+        <is>
+          <t>Geoapify Geocoding API</t>
+        </is>
+      </c>
+      <c r="F472" t="inlineStr">
+        <is>
+          <t>https://api.geoapify.com/v1/geocode/search?text=Elliot's Beach, Chennai, Tamil Nadu, India&amp;filter=circle:80.2763077,13.0825901,30000&amp;bias=proximity:80.2763077,13.0825901&amp;limit=5&amp;format=json</t>
+        </is>
+      </c>
+      <c r="G472" t="inlineStr">
+        <is>
+          <t>2026-09-14T04:15:56.798328+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>step02_coordinates</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>P12</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>coordinates</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>Selected via primary query: rank.confidence=1.000, 9.43km from Chennai Central (within 40.0km validation threshold), geoapify place_id=519677d5036611544059d0978345eafe2940f00101f9018443da0000000000c0020192030d456c6c696f7473204265616368.</t>
+        </is>
+      </c>
+      <c r="E473" t="inlineStr">
+        <is>
+          <t>Geoapify Geocoding API</t>
+        </is>
+      </c>
+      <c r="F473" t="inlineStr">
+        <is>
+          <t>https://api.geoapify.com/v1/geocode/search?text=Besant Nagar Beach, Chennai, Tamil Nadu, India&amp;filter=circle:80.2763077,13.0825901,30000&amp;bias=proximity:80.2763077,13.0825901&amp;limit=5&amp;format=json</t>
+        </is>
+      </c>
+      <c r="G473" t="inlineStr">
+        <is>
+          <t>2026-09-14T04:15:56.799336+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>step02_coordinates</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>P13</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>coordinates</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>No Geoapify result within 40.0km of Chennai Central for 1 query tried ('DakshinaChitra, Chennai, Tamil Nadu, India'). Coordinates intentionally left blank rather than guessed; needs manual review.</t>
+        </is>
+      </c>
+      <c r="E474" t="inlineStr">
+        <is>
+          <t>Geoapify Geocoding API</t>
+        </is>
+      </c>
+      <c r="F474" t="inlineStr">
+        <is>
+          <t>https://api.geoapify.com/v1/geocode/search?text=DakshinaChitra, Chennai, Tamil Nadu, India&amp;filter=circle:80.2763077,13.0825901,30000&amp;bias=proximity:80.2763077,13.0825901&amp;limit=5&amp;format=json</t>
+        </is>
+      </c>
+      <c r="G474" t="inlineStr">
+        <is>
+          <t>2026-09-14T04:15:56.800325+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>step02_coordinates</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>P14</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>coordinates</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>Selected via primary query: rank.confidence=1.000, 17.95km from Chennai Central (within 40.0km validation threshold), geoapify place_id=51fd3e2d501c105440592692431f87d82940f00103f901a6499fea00000000c0020192031c43686f6c616d616e64616c2041727469737473272056696c6c616765.</t>
+        </is>
+      </c>
+      <c r="E475" t="inlineStr">
+        <is>
+          <t>Geoapify Geocoding API</t>
+        </is>
+      </c>
+      <c r="F475" t="inlineStr">
+        <is>
+          <t>https://api.geoapify.com/v1/geocode/search?text=Cholamandal Artists' Village, Chennai, Tamil Nadu, India&amp;filter=circle:80.2763077,13.0825901,30000&amp;bias=proximity:80.2763077,13.0825901&amp;limit=5&amp;format=json</t>
+        </is>
+      </c>
+      <c r="G475" t="inlineStr">
+        <is>
+          <t>2026-09-14T04:15:56.801317+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>step02_coordinates</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>P15</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>coordinates</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>No Geoapify result within 40.0km of Chennai Central for 2 queries tried ('Vivekananda House, Chennai, Tamil Nadu, India'; 'Vivekanandar Illam, Chennai, India'). Coordinates intentionally left blank rather than guessed; needs manual review.</t>
+        </is>
+      </c>
+      <c r="E476" t="inlineStr">
+        <is>
+          <t>Geoapify Geocoding API</t>
+        </is>
+      </c>
+      <c r="F476" t="inlineStr">
+        <is>
+          <t>https://api.geoapify.com/v1/geocode/search?text=Vivekanandar Illam, Chennai, India&amp;filter=circle:80.2763077,13.0825901,30000&amp;bias=proximity:80.2763077,13.0825901&amp;limit=5&amp;format=json</t>
+        </is>
+      </c>
+      <c r="G476" t="inlineStr">
+        <is>
+          <t>2026-09-14T04:15:56.802323+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>step02_coordinates</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>P16</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>coordinates</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>Selected via primary query: rank.confidence=1.000, 3.81km from Chennai Central (within 40.0km validation threshold), geoapify place_id=517b6af5d555105440590219f0e8351c2a40f00102f9017542f90c00000000c0020192031654686f7573616e64204c6967687473204d6f73717565.</t>
+        </is>
+      </c>
+      <c r="E477" t="inlineStr">
+        <is>
+          <t>Geoapify Geocoding API</t>
+        </is>
+      </c>
+      <c r="F477" t="inlineStr">
+        <is>
+          <t>https://api.geoapify.com/v1/geocode/search?text=Thousand Lights Mosque, Chennai, Tamil Nadu, India&amp;filter=circle:80.2763077,13.0825901,30000&amp;bias=proximity:80.2763077,13.0825901&amp;limit=5&amp;format=json</t>
+        </is>
+      </c>
+      <c r="G477" t="inlineStr">
+        <is>
+          <t>2026-09-14T04:15:56.803327+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>step02_coordinates</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>P17</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>coordinates</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>Selected via primary query: rank.confidence=0.810, 3.19km from Chennai Central (within 40.0km validation threshold), geoapify place_id=5123a69fcbaf11544059a3772ae09e1b2a40f00101f90196cf530000000000c002019203234172756c6d6967752050617274686173617261746879205377616d792054656d706c65.</t>
+        </is>
+      </c>
+      <c r="E478" t="inlineStr">
+        <is>
+          <t>Geoapify Geocoding API</t>
+        </is>
+      </c>
+      <c r="F478" t="inlineStr">
+        <is>
+          <t>https://api.geoapify.com/v1/geocode/search?text=Parthasarathy Temple, Chennai, Tamil Nadu, India&amp;filter=circle:80.2763077,13.0825901,30000&amp;bias=proximity:80.2763077,13.0825901&amp;limit=5&amp;format=json</t>
+        </is>
+      </c>
+      <c r="G478" t="inlineStr">
+        <is>
+          <t>2026-09-14T04:15:56.804323+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>step02_coordinates</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>P18</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>coordinates</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>Selected via primary query: rank.confidence=0.900, 7.48km from Chennai Central (within 40.0km validation threshold), geoapify place_id=513d8dc580b60d544059726083cf201b2a40f00102f90139c2a70100000000c0020192031e5661646170616c616e69204d75727567616e2054656d706c6520506f6e64.</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr">
+        <is>
+          <t>Geoapify Geocoding API</t>
+        </is>
+      </c>
+      <c r="F479" t="inlineStr">
+        <is>
+          <t>https://api.geoapify.com/v1/geocode/search?text=Vadapalani Murugan Temple, Chennai, Tamil Nadu, India&amp;filter=circle:80.2763077,13.0825901,30000&amp;bias=proximity:80.2763077,13.0825901&amp;limit=5&amp;format=json</t>
+        </is>
+      </c>
+      <c r="G479" t="inlineStr">
+        <is>
+          <t>2026-09-14T04:15:56.805279+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>step02_coordinates</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>P19</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>coordinates</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>Selected via primary query: rank.confidence=1.000, 2.96km from Chennai Central (within 40.0km validation threshold), geoapify place_id=510d326e0fe71054405986a9d2bb1d1e2a40f00102f901dbfff80c00000000c0020192031345787072657373204176656e7565204d616c6c.</t>
+        </is>
+      </c>
+      <c r="E480" t="inlineStr">
+        <is>
+          <t>Geoapify Geocoding API</t>
+        </is>
+      </c>
+      <c r="F480" t="inlineStr">
+        <is>
+          <t>https://api.geoapify.com/v1/geocode/search?text=Express Avenue, Chennai, Tamil Nadu, India&amp;filter=circle:80.2763077,13.0825901,30000&amp;bias=proximity:80.2763077,13.0825901&amp;limit=5&amp;format=json</t>
+        </is>
+      </c>
+      <c r="G480" t="inlineStr">
+        <is>
+          <t>2026-09-14T04:15:56.806319+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>step02_coordinates</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>P20</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>coordinates</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>Selected via primary query: rank.confidence=1.000, 28.74km from Chennai Central (within 40.0km validation threshold), geoapify place_id=51d472b1b3b20f544059bc56e7bdd6a62940f00102f90198111d0200000000c002019203104d474d2044697a7a656520576f726c64.</t>
+        </is>
+      </c>
+      <c r="E481" t="inlineStr">
+        <is>
+          <t>Geoapify Geocoding API</t>
+        </is>
+      </c>
+      <c r="F481" t="inlineStr">
+        <is>
+          <t>https://api.geoapify.com/v1/geocode/search?text=MGM Dizzee World, Chennai, Tamil Nadu, India&amp;filter=circle:80.2763077,13.0825901,30000&amp;bias=proximity:80.2763077,13.0825901&amp;limit=5&amp;format=json</t>
+        </is>
+      </c>
+      <c r="G481" t="inlineStr">
+        <is>
+          <t>2026-09-14T04:15:56.807327+00:00</t>
         </is>
       </c>
     </row>

--- a/data/BayesTrip_Data.xlsx
+++ b/data/BayesTrip_Data.xlsx
@@ -1131,7 +1131,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-09-14T04:15:18.389382+00:00</t>
+          <t>2026-09-14T05:44:52.659372+00:00</t>
         </is>
       </c>
       <c r="M2" t="n">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-09-14T04:15:20.230531+00:00</t>
+          <t>2026-09-14T05:44:54.493431+00:00</t>
         </is>
       </c>
       <c r="M3" t="n">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-09-14T04:15:21.788338+00:00</t>
+          <t>2026-09-14T05:44:56.212569+00:00</t>
         </is>
       </c>
       <c r="M4" t="n">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-09-14T04:15:25.767302+00:00</t>
+          <t>2026-09-14T05:45:00.587515+00:00</t>
         </is>
       </c>
       <c r="M5" t="n">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-09-14T04:15:27.500956+00:00</t>
+          <t>2026-09-14T05:45:02.321747+00:00</t>
         </is>
       </c>
       <c r="M6" t="n">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-09-14T04:15:29.140545+00:00</t>
+          <t>2026-09-14T05:45:03.915607+00:00</t>
         </is>
       </c>
       <c r="M7" t="n">
@@ -1527,7 +1527,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-09-14T04:15:33.032758+00:00</t>
+          <t>2026-09-14T05:45:08.060318+00:00</t>
         </is>
       </c>
       <c r="M8" t="n">
@@ -1593,7 +1593,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-09-14T04:15:34.508015+00:00</t>
+          <t>2026-09-14T05:45:09.789996+00:00</t>
         </is>
       </c>
       <c r="M9" t="n">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-09-14T04:15:36.206548+00:00</t>
+          <t>2026-09-14T05:45:11.437109+00:00</t>
         </is>
       </c>
       <c r="M10" t="n">
@@ -1725,7 +1725,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-09-14T04:15:37.950994+00:00</t>
+          <t>2026-09-14T05:45:12.910378+00:00</t>
         </is>
       </c>
       <c r="M11" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-09-14T04:15:39.859108+00:00</t>
+          <t>2026-09-14T05:45:14.647489+00:00</t>
         </is>
       </c>
       <c r="M12" t="n">
@@ -1857,7 +1857,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-09-14T04:15:41.528795+00:00</t>
+          <t>2026-09-14T05:45:16.321379+00:00</t>
         </is>
       </c>
       <c r="M13" t="n">
@@ -1882,8 +1882,34 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>DakshinaChitra, Chennai, Tamil Nadu, India</t>
-        </is>
+          <t>Dakshin Chitra, Muttukadu, Tamil Nadu, India</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Dakshin Chitra, East Coast Road, Muttukaadu, Kelambakkam - 603112, TN, India</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Kelambakkam</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tamil Nadu</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>12.8227449</v>
+      </c>
+      <c r="I14" t="n">
+        <v>80.2420326</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1892,22 +1918,20 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>https://api.geoapify.com/v1/geocode/search?text=DakshinaChitra, Chennai, Tamil Nadu, India&amp;filter=circle:80.2763077,13.0825901,30000&amp;bias=proximity:80.2763077,13.0825901&amp;limit=5&amp;format=json</t>
+          <t>https://api.geoapify.com/v1/geocode/search?text=Dakshin Chitra, Muttukadu, Tamil Nadu, India&amp;filter=circle:80.2763077,13.0825901,30000&amp;bias=proximity:80.2763077,13.0825901&amp;limit=5&amp;format=json</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-09-14T04:15:43.473686+00:00</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>needs_manual_review</t>
-        </is>
+          <t>2026-09-14T05:45:19.659528+00:00</t>
+        </is>
+      </c>
+      <c r="M14" t="n">
+        <v>0.8100000000000001</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>No Geoapify result within 40.0km of Chennai Central for 1 query tried ('DakshinaChitra, Chennai, Tamil Nadu, India'). Coordinates intentionally left blank rather than guessed; needs manual review.</t>
+          <t>Selected via fallback query: rank.confidence=0.810, 29.13km from Chennai Central (within 40.0km validation threshold), geoapify place_id=5137644d767d0f544059cee6ccd13ea52940f00101f901da6d2e0100000000c0020192030e44616b7368696e20436869747261.</t>
         </is>
       </c>
     </row>
@@ -1965,7 +1989,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-09-14T04:15:45.227749+00:00</t>
+          <t>2026-09-14T05:45:21.072025+00:00</t>
         </is>
       </c>
       <c r="M15" t="n">
@@ -1990,8 +2014,34 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Vivekanandar Illam, Chennai, India</t>
-        </is>
+          <t>Ice House, Chennai, Tamil Nadu, India</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Ice House stop, Kamarajar Promenade, Zone 9 Teynampet, Chennai - 600005, TN, India</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tamil Nadu</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>13.049045</v>
+      </c>
+      <c r="I16" t="n">
+        <v>80.2804835</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -2000,22 +2050,20 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>https://api.geoapify.com/v1/geocode/search?text=Vivekanandar Illam, Chennai, India&amp;filter=circle:80.2763077,13.0825901,30000&amp;bias=proximity:80.2763077,13.0825901&amp;limit=5&amp;format=json</t>
+          <t>https://api.geoapify.com/v1/geocode/search?text=Ice House, Chennai, Tamil Nadu, India&amp;filter=circle:80.2763077,13.0825901,30000&amp;bias=proximity:80.2763077,13.0825901&amp;limit=5&amp;format=json</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-09-14T04:15:48.458871+00:00</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>needs_manual_review</t>
-        </is>
+          <t>2026-09-14T05:45:27.508017+00:00</t>
+        </is>
+      </c>
+      <c r="M16" t="n">
+        <v>0.9</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>No Geoapify result within 40.0km of Chennai Central for 2 queries tried ('Vivekananda House, Chennai, Tamil Nadu, India'; 'Vivekanandar Illam, Chennai, India'). Coordinates intentionally left blank rather than guessed; needs manual review.</t>
+          <t>Selected via fallback query: rank.confidence=0.900, 3.76km from Chennai Central (within 40.0km validation threshold), geoapify place_id=5154e41071f3115440598c101e6d1c192a40f00103f901c94f3c1500000000c0020192030e49636520486f7573652073746f70.</t>
         </is>
       </c>
     </row>
@@ -2073,7 +2121,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-09-14T04:15:50.036275+00:00</t>
+          <t>2026-09-14T05:45:29.349775+00:00</t>
         </is>
       </c>
       <c r="M17" t="n">
@@ -2139,7 +2187,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-09-14T04:15:51.849268+00:00</t>
+          <t>2026-09-14T05:45:30.988366+00:00</t>
         </is>
       </c>
       <c r="M18" t="n">
@@ -2205,7 +2253,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-09-14T04:15:53.525085+00:00</t>
+          <t>2026-09-14T05:45:32.729528+00:00</t>
         </is>
       </c>
       <c r="M19" t="n">
@@ -2271,7 +2319,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-09-14T04:15:55.045686+00:00</t>
+          <t>2026-09-14T05:45:34.259707+00:00</t>
         </is>
       </c>
       <c r="M20" t="n">
@@ -2337,7 +2385,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-09-14T04:15:56.779222+00:00</t>
+          <t>2026-09-14T05:45:35.904736+00:00</t>
         </is>
       </c>
       <c r="M21" t="n">

--- a/data/BayesTrip_Data.xlsx
+++ b/data/BayesTrip_Data.xlsx
@@ -2408,7 +2408,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:Q21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2419,22 +2419,82 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>place_name</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>travel_time_seconds</t>
+          <t>start_location</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>raw_score</t>
+          <t>start_latitude</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>pi</t>
+          <t>start_longitude</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>place_latitude</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>place_longitude</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>distance_km</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>travel_time_min</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>raw_accessibility_score</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>distance_method</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>source_url</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>retrieved_at</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>justification</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>confidence</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>initial_probability</t>
         </is>
       </c>
     </row>
@@ -2449,14 +2509,64 @@
           <t>Marina Beach</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>313.5</v>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Chennai Central Railway Station</t>
+        </is>
       </c>
       <c r="D2" t="n">
-        <v>0.003189792663476874</v>
+        <v>13.0825901</v>
       </c>
       <c r="E2" t="n">
-        <v>0.07560111097594464</v>
+        <v>80.2763077</v>
+      </c>
+      <c r="F2" t="n">
+        <v>13.0532752</v>
+      </c>
+      <c r="G2" t="n">
+        <v>80.28331059999999</v>
+      </c>
+      <c r="H2" t="n">
+        <v>4.181</v>
+      </c>
+      <c r="I2" t="n">
+        <v>5.225</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.1910219675262655</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>OSRM road routing (table service, driving profile): distance and travel time both from the same OSRM response</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>OSRM public routing API (table service)</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://router.project-osrm.org/table/v1/driving/</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2026-09-14T07:07:34.074498+00:00</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Destination is approximately 4.18 km (5.2 min driving) from Chennai Central Railway Station via OSRM road routing. The accessibility score is calculated using the predefined inverse-travel-time formula (1 / (travel_time_min + 0.01)), then normalized across all 20 destinations.</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.07561240811253077</v>
       </c>
     </row>
     <row r="3">
@@ -2470,14 +2580,64 @@
           <t>Fort St. George</t>
         </is>
       </c>
-      <c r="C3" t="n">
-        <v>162.7</v>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Chennai Central Railway Station</t>
+        </is>
       </c>
       <c r="D3" t="n">
-        <v>0.006146281499692687</v>
+        <v>13.0825901</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1456727000058921</v>
+        <v>80.2763077</v>
+      </c>
+      <c r="F3" t="n">
+        <v>13.0798617</v>
+      </c>
+      <c r="G3" t="n">
+        <v>80.2846692</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.508</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.712</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.3673769287288758</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>OSRM road routing (table service, driving profile): distance and travel time both from the same OSRM response</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>OSRM public routing API (table service)</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://router.project-osrm.org/table/v1/driving/</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2026-09-14T07:07:34.074498+00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Destination is approximately 1.51 km (2.7 min driving) from Chennai Central Railway Station via OSRM road routing. The accessibility score is calculated using the predefined inverse-travel-time formula (1 / (travel_time_min + 0.01)), then normalized across all 20 destinations.</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.1454191610834308</v>
       </c>
     </row>
     <row r="4">
@@ -2491,14 +2651,64 @@
           <t>Kapaleeshwarar Temple</t>
         </is>
       </c>
-      <c r="C4" t="n">
-        <v>536.3</v>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Chennai Central Railway Station</t>
+        </is>
       </c>
       <c r="D4" t="n">
-        <v>0.001864628006712661</v>
+        <v>13.0825901</v>
       </c>
       <c r="E4" t="n">
-        <v>0.04419345196897007</v>
+        <v>80.2763077</v>
+      </c>
+      <c r="F4" t="n">
+        <v>13.0334291</v>
+      </c>
+      <c r="G4" t="n">
+        <v>80.2686576</v>
+      </c>
+      <c r="H4" t="n">
+        <v>6.92</v>
+      </c>
+      <c r="I4" t="n">
+        <v>8.94</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.111731843575419</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>OSRM road routing (table service, driving profile): distance and travel time both from the same OSRM response</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>OSRM public routing API (table service)</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://router.project-osrm.org/table/v1/driving/</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2026-09-14T07:07:34.074498+00:00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Destination is approximately 6.92 km (8.9 min driving) from Chennai Central Railway Station via OSRM road routing. The accessibility score is calculated using the predefined inverse-travel-time formula (1 / (travel_time_min + 0.01)), then normalized across all 20 destinations.</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.04422692251051381</v>
       </c>
     </row>
     <row r="5">
@@ -2512,14 +2722,64 @@
           <t>San Thome Basilica</t>
         </is>
       </c>
-      <c r="C5" t="n">
-        <v>451.4</v>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Chennai Central Railway Station</t>
+        </is>
       </c>
       <c r="D5" t="n">
-        <v>0.002215330084182543</v>
+        <v>13.0825901</v>
       </c>
       <c r="E5" t="n">
-        <v>0.05250542377261553</v>
+        <v>80.2763077</v>
+      </c>
+      <c r="F5" t="n">
+        <v>13.0335889</v>
+      </c>
+      <c r="G5" t="n">
+        <v>80.2777851</v>
+      </c>
+      <c r="H5" t="n">
+        <v>6.798</v>
+      </c>
+      <c r="I5" t="n">
+        <v>7.523</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.132749236691889</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>OSRM road routing (table service, driving profile): distance and travel time both from the same OSRM response</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>OSRM public routing API (table service)</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://router.project-osrm.org/table/v1/driving/</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2026-09-14T07:07:34.074498+00:00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Destination is approximately 6.80 km (7.5 min driving) from Chennai Central Railway Station via OSRM road routing. The accessibility score is calculated using the predefined inverse-travel-time formula (1 / (travel_time_min + 0.01)), then normalized across all 20 destinations.</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.05254625733029319</v>
       </c>
     </row>
     <row r="6">
@@ -2533,14 +2793,64 @@
           <t>Government Museum, Chennai</t>
         </is>
       </c>
-      <c r="C6" t="n">
-        <v>291</v>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Chennai Central Railway Station</t>
+        </is>
       </c>
       <c r="D6" t="n">
-        <v>0.003436426116838488</v>
+        <v>13.0825901</v>
       </c>
       <c r="E6" t="n">
-        <v>0.08144655770088882</v>
+        <v>80.2763077</v>
+      </c>
+      <c r="F6" t="n">
+        <v>13.0712808</v>
+      </c>
+      <c r="G6" t="n">
+        <v>80.25704330000001</v>
+      </c>
+      <c r="H6" t="n">
+        <v>3.672</v>
+      </c>
+      <c r="I6" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.205761316872428</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>OSRM road routing (table service, driving profile): distance and travel time both from the same OSRM response</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>OSRM public routing API (table service)</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://router.project-osrm.org/table/v1/driving/</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2026-09-14T07:07:34.074498+00:00</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Destination is approximately 3.67 km (4.8 min driving) from Chennai Central Railway Station via OSRM road routing. The accessibility score is calculated using the predefined inverse-travel-time formula (1 / (travel_time_min + 0.01)), then normalized across all 20 destinations.</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.08144669886195445</v>
       </c>
     </row>
     <row r="7">
@@ -2554,14 +2864,64 @@
           <t>Guindy National Park</t>
         </is>
       </c>
-      <c r="C7" t="n">
-        <v>1129.9</v>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Chennai Central Railway Station</t>
+        </is>
       </c>
       <c r="D7" t="n">
-        <v>0.0008850340738118417</v>
+        <v>13.0825901</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02097614681915094</v>
+        <v>80.2763077</v>
+      </c>
+      <c r="F7" t="n">
+        <v>13.000005</v>
+      </c>
+      <c r="G7" t="n">
+        <v>80.22804480000001</v>
+      </c>
+      <c r="H7" t="n">
+        <v>14.129</v>
+      </c>
+      <c r="I7" t="n">
+        <v>18.832</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.05307292219509606</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>OSRM road routing (table service, driving profile): distance and travel time both from the same OSRM response</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>OSRM public routing API (table service)</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://router.project-osrm.org/table/v1/driving/</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2026-09-14T07:07:34.074498+00:00</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Destination is approximately 14.13 km (18.8 min driving) from Chennai Central Railway Station via OSRM road routing. The accessibility score is calculated using the predefined inverse-travel-time formula (1 / (travel_time_min + 0.01)), then normalized across all 20 destinations.</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.02100790555509492</v>
       </c>
     </row>
     <row r="8">
@@ -2575,14 +2935,64 @@
           <t>Arignar Anna Zoological Park (Vandalur Zoo)</t>
         </is>
       </c>
-      <c r="C8" t="n">
-        <v>2185.4</v>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Chennai Central Railway Station</t>
+        </is>
       </c>
       <c r="D8" t="n">
-        <v>0.0004575821359934108</v>
+        <v>13.0825901</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01084513054404624</v>
+        <v>80.2763077</v>
+      </c>
+      <c r="F8" t="n">
+        <v>12.8834325</v>
+      </c>
+      <c r="G8" t="n">
+        <v>80.0915303</v>
+      </c>
+      <c r="H8" t="n">
+        <v>39.288</v>
+      </c>
+      <c r="I8" t="n">
+        <v>38.163</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.02619652634060724</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>OSRM road routing (table service, driving profile): distance and travel time both from the same OSRM response</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>OSRM public routing API (table service)</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://router.project-osrm.org/table/v1/driving/</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2026-09-14T07:07:34.074498+00:00</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Destination is approximately 39.29 km (38.2 min driving) from Chennai Central Railway Station via OSRM road routing. The accessibility score is calculated using the predefined inverse-travel-time formula (1 / (travel_time_min + 0.01)), then normalized across all 20 destinations.</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.0103693960775705</v>
       </c>
     </row>
     <row r="9">
@@ -2596,14 +3006,64 @@
           <t>Valluvar Kottam</t>
         </is>
       </c>
-      <c r="C9" t="n">
-        <v>463.2</v>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Chennai Central Railway Station</t>
+        </is>
       </c>
       <c r="D9" t="n">
-        <v>0.002158894645941278</v>
+        <v>13.0825901</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0511678503690817</v>
+        <v>80.2763077</v>
+      </c>
+      <c r="F9" t="n">
+        <v>13.05383</v>
+      </c>
+      <c r="G9" t="n">
+        <v>80.2423007</v>
+      </c>
+      <c r="H9" t="n">
+        <v>6.924</v>
+      </c>
+      <c r="I9" t="n">
+        <v>7.525</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.13271400132714</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>OSRM road routing (table service, driving profile): distance and travel time both from the same OSRM response</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>OSRM public routing API (table service)</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://router.project-osrm.org/table/v1/driving/</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2026-09-14T07:07:34.074498+00:00</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Destination is approximately 6.92 km (7.5 min driving) from Chennai Central Railway Station via OSRM road routing. The accessibility score is calculated using the predefined inverse-travel-time formula (1 / (travel_time_min + 0.01)), then normalized across all 20 destinations.</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.05253231008216305</v>
       </c>
     </row>
     <row r="10">
@@ -2617,14 +3077,64 @@
           <t>Birla Planetarium</t>
         </is>
       </c>
-      <c r="C10" t="n">
-        <v>924.1</v>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Chennai Central Railway Station</t>
+        </is>
       </c>
       <c r="D10" t="n">
-        <v>0.001082133968185261</v>
+        <v>13.0825901</v>
       </c>
       <c r="E10" t="n">
-        <v>0.02564760122384876</v>
+        <v>80.2763077</v>
+      </c>
+      <c r="F10" t="n">
+        <v>13.0119591</v>
+      </c>
+      <c r="G10" t="n">
+        <v>80.2440161</v>
+      </c>
+      <c r="H10" t="n">
+        <v>10.59</v>
+      </c>
+      <c r="I10" t="n">
+        <v>15.402</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.06488450558006749</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>OSRM road routing (table service, driving profile): distance and travel time both from the same OSRM response</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>OSRM public routing API (table service)</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://router.project-osrm.org/table/v1/driving/</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2026-09-14T07:07:34.074498+00:00</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Destination is approximately 10.59 km (15.4 min driving) from Chennai Central Railway Station via OSRM road routing. The accessibility score is calculated using the predefined inverse-travel-time formula (1 / (travel_time_min + 0.01)), then normalized across all 20 destinations.</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.02568329590378268</v>
       </c>
     </row>
     <row r="11">
@@ -2638,14 +3148,64 @@
           <t>Semmozhi Poonga</t>
         </is>
       </c>
-      <c r="C11" t="n">
-        <v>398.8</v>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Chennai Central Railway Station</t>
+        </is>
       </c>
       <c r="D11" t="n">
-        <v>0.002507522567703109</v>
+        <v>13.0825901</v>
       </c>
       <c r="E11" t="n">
-        <v>0.05943066271554324</v>
+        <v>80.2763077</v>
+      </c>
+      <c r="F11" t="n">
+        <v>13.0506767</v>
+      </c>
+      <c r="G11" t="n">
+        <v>80.2514735</v>
+      </c>
+      <c r="H11" t="n">
+        <v>6.119</v>
+      </c>
+      <c r="I11" t="n">
+        <v>6.647</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.1502178158329578</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>OSRM road routing (table service, driving profile): distance and travel time both from the same OSRM response</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>OSRM public routing API (table service)</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://router.project-osrm.org/table/v1/driving/</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2026-09-14T07:07:34.074498+00:00</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Destination is approximately 6.12 km (6.6 min driving) from Chennai Central Railway Station via OSRM road routing. The accessibility score is calculated using the predefined inverse-travel-time formula (1 / (travel_time_min + 0.01)), then normalized across all 20 destinations.</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.05946086171985858</v>
       </c>
     </row>
     <row r="12">
@@ -2659,14 +3219,64 @@
           <t>Elliot's Beach</t>
         </is>
       </c>
-      <c r="C12" t="n">
-        <v>942.3</v>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Chennai Central Railway Station</t>
+        </is>
       </c>
       <c r="D12" t="n">
-        <v>0.001061233152923697</v>
+        <v>13.0825901</v>
       </c>
       <c r="E12" t="n">
-        <v>0.02515223208209556</v>
+        <v>80.2763077</v>
+      </c>
+      <c r="F12" t="n">
+        <v>13.0001673</v>
+      </c>
+      <c r="G12" t="n">
+        <v>80.2711805</v>
+      </c>
+      <c r="H12" t="n">
+        <v>13.136</v>
+      </c>
+      <c r="I12" t="n">
+        <v>14.912</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.06701514542286556</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>OSRM road routing (table service, driving profile): distance and travel time both from the same OSRM response</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>OSRM public routing API (table service)</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>https://router.project-osrm.org/table/v1/driving/</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2026-09-14T07:07:34.074498+00:00</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Destination is approximately 13.14 km (14.9 min driving) from Chennai Central Railway Station via OSRM road routing. The accessibility score is calculated using the predefined inverse-travel-time formula (1 / (travel_time_min + 0.01)), then normalized across all 20 destinations.</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.02652666911064861</v>
       </c>
     </row>
     <row r="13">
@@ -2680,14 +3290,64 @@
           <t>Besant Nagar Beach</t>
         </is>
       </c>
-      <c r="C13" t="n">
-        <v>951.4</v>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Chennai Central Railway Station</t>
+        </is>
       </c>
       <c r="D13" t="n">
-        <v>0.001051082615093546</v>
+        <v>13.0825901</v>
       </c>
       <c r="E13" t="n">
-        <v>0.02491165470985773</v>
+        <v>80.2763077</v>
+      </c>
+      <c r="F13" t="n">
+        <v>12.9978811</v>
+      </c>
+      <c r="G13" t="n">
+        <v>80.2718515</v>
+      </c>
+      <c r="H13" t="n">
+        <v>13.569</v>
+      </c>
+      <c r="I13" t="n">
+        <v>15.857</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.06302388605281402</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>OSRM road routing (table service, driving profile): distance and travel time both from the same OSRM response</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>OSRM public routing API (table service)</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>https://router.project-osrm.org/table/v1/driving/</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>2026-09-14T07:07:34.074498+00:00</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Destination is approximately 13.57 km (15.9 min driving) from Chennai Central Railway Station via OSRM road routing. The accessibility score is calculated using the predefined inverse-travel-time formula (1 / (travel_time_min + 0.01)), then normalized across all 20 destinations.</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.02494680509668485</v>
       </c>
     </row>
     <row r="14">
@@ -2701,14 +3361,64 @@
           <t>DakshinaChitra</t>
         </is>
       </c>
-      <c r="C14" t="n">
-        <v>2010.7</v>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Chennai Central Railway Station</t>
+        </is>
       </c>
       <c r="D14" t="n">
-        <v>0.0004973392350922564</v>
+        <v>13.0825901</v>
       </c>
       <c r="E14" t="n">
-        <v>0.01178741149398649</v>
+        <v>80.2763077</v>
+      </c>
+      <c r="F14" t="n">
+        <v>12.8227449</v>
+      </c>
+      <c r="G14" t="n">
+        <v>80.2420326</v>
+      </c>
+      <c r="H14" t="n">
+        <v>32.046</v>
+      </c>
+      <c r="I14" t="n">
+        <v>33.098</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.03020418025854778</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>OSRM road routing (table service, driving profile): distance and travel time both from the same OSRM response</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>OSRM public routing API (table service)</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>https://router.project-osrm.org/table/v1/driving/</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2026-09-14T07:07:34.074498+00:00</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Destination is approximately 32.05 km (33.1 min driving) from Chennai Central Railway Station via OSRM road routing. The accessibility score is calculated using the predefined inverse-travel-time formula (1 / (travel_time_min + 0.01)), then normalized across all 20 destinations.</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.01195574956110603</v>
       </c>
     </row>
     <row r="15">
@@ -2722,14 +3432,64 @@
           <t>Cholamandal Artists' Village</t>
         </is>
       </c>
-      <c r="C15" t="n">
-        <v>1372</v>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Chennai Central Railway Station</t>
+        </is>
       </c>
       <c r="D15" t="n">
-        <v>0.0007288629737609329</v>
+        <v>13.0825901</v>
       </c>
       <c r="E15" t="n">
-        <v>0.01727474365230222</v>
+        <v>80.2763077</v>
+      </c>
+      <c r="F15" t="n">
+        <v>12.9229059</v>
+      </c>
+      <c r="G15" t="n">
+        <v>80.25172809999999</v>
+      </c>
+      <c r="H15" t="n">
+        <v>20.776</v>
+      </c>
+      <c r="I15" t="n">
+        <v>22.408</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.04460701222232134</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>OSRM road routing (table service, driving profile): distance and travel time both from the same OSRM response</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>OSRM public routing API (table service)</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>https://router.project-osrm.org/table/v1/driving/</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2026-09-14T07:07:34.074498+00:00</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Destination is approximately 20.78 km (22.4 min driving) from Chennai Central Railway Station via OSRM road routing. The accessibility score is calculated using the predefined inverse-travel-time formula (1 / (travel_time_min + 0.01)), then normalized across all 20 destinations.</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.01765683631319023</v>
       </c>
     </row>
     <row r="16">
@@ -2743,14 +3503,64 @@
           <t>Vivekananda House</t>
         </is>
       </c>
-      <c r="C16" t="n">
-        <v>323.7</v>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Chennai Central Railway Station</t>
+        </is>
       </c>
       <c r="D16" t="n">
-        <v>0.003089280197713933</v>
+        <v>13.0825901</v>
       </c>
       <c r="E16" t="n">
-        <v>0.07321887022230042</v>
+        <v>80.2763077</v>
+      </c>
+      <c r="F16" t="n">
+        <v>13.049045</v>
+      </c>
+      <c r="G16" t="n">
+        <v>80.2804835</v>
+      </c>
+      <c r="H16" t="n">
+        <v>5.291</v>
+      </c>
+      <c r="I16" t="n">
+        <v>5.345</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.1867413632119514</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>OSRM road routing (table service, driving profile): distance and travel time both from the same OSRM response</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>OSRM public routing API (table service)</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>https://router.project-osrm.org/table/v1/driving/</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>2026-09-14T07:07:34.074498+00:00</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Destination is approximately 5.29 km (5.3 min driving) from Chennai Central Railway Station via OSRM road routing. The accessibility score is calculated using the predefined inverse-travel-time formula (1 / (travel_time_min + 0.01)), then normalized across all 20 destinations.</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.07391801241253007</v>
       </c>
     </row>
     <row r="17">
@@ -2764,14 +3574,64 @@
           <t>Thousand Lights Mosque</t>
         </is>
       </c>
-      <c r="C17" t="n">
-        <v>296.6</v>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Chennai Central Railway Station</t>
+        </is>
       </c>
       <c r="D17" t="n">
-        <v>0.003371544167228591</v>
+        <v>13.0825901</v>
       </c>
       <c r="E17" t="n">
-        <v>0.07990879396816805</v>
+        <v>80.2763077</v>
+      </c>
+      <c r="F17" t="n">
+        <v>13.0550988</v>
+      </c>
+      <c r="G17" t="n">
+        <v>80.255239</v>
+      </c>
+      <c r="H17" t="n">
+        <v>4.733</v>
+      </c>
+      <c r="I17" t="n">
+        <v>4.943</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.2018978396931153</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>OSRM road routing (table service, driving profile): distance and travel time both from the same OSRM response</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>OSRM public routing API (table service)</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>https://router.project-osrm.org/table/v1/driving/</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>2026-09-14T07:07:34.074498+00:00</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Destination is approximately 4.73 km (4.9 min driving) from Chennai Central Railway Station via OSRM road routing. The accessibility score is calculated using the predefined inverse-travel-time formula (1 / (travel_time_min + 0.01)), then normalized across all 20 destinations.</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.07991741499477056</v>
       </c>
     </row>
     <row r="18">
@@ -2785,14 +3645,64 @@
           <t>Parthasarathy Temple</t>
         </is>
       </c>
-      <c r="C18" t="n">
-        <v>318.3</v>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Chennai Central Railway Station</t>
+        </is>
       </c>
       <c r="D18" t="n">
-        <v>0.003141690229343387</v>
+        <v>13.0825901</v>
       </c>
       <c r="E18" t="n">
-        <v>0.07446103767187762</v>
+        <v>80.2763077</v>
+      </c>
+      <c r="F18" t="n">
+        <v>13.0539465</v>
+      </c>
+      <c r="G18" t="n">
+        <v>80.2763547</v>
+      </c>
+      <c r="H18" t="n">
+        <v>4.404</v>
+      </c>
+      <c r="I18" t="n">
+        <v>5.572</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.1791472590469366</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>OSRM road routing (table service, driving profile): distance and travel time both from the same OSRM response</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>OSRM public routing API (table service)</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>https://router.project-osrm.org/table/v1/driving/</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>2026-09-14T07:07:34.074498+00:00</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Destination is approximately 4.40 km (5.6 min driving) from Chennai Central Railway Station via OSRM road routing. The accessibility score is calculated using the predefined inverse-travel-time formula (1 / (travel_time_min + 0.01)), then normalized across all 20 destinations.</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.07091203089736628</v>
       </c>
     </row>
     <row r="19">
@@ -2806,14 +3716,64 @@
           <t>Vadapalani Murugan Temple</t>
         </is>
       </c>
-      <c r="C19" t="n">
-        <v>735.7</v>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Chennai Central Railway Station</t>
+        </is>
       </c>
       <c r="D19" t="n">
-        <v>0.001359249694168819</v>
+        <v>13.0825901</v>
       </c>
       <c r="E19" t="n">
-        <v>0.03221550671599652</v>
+        <v>80.2763077</v>
+      </c>
+      <c r="F19" t="n">
+        <v>13.0529847</v>
+      </c>
+      <c r="G19" t="n">
+        <v>80.21426409999999</v>
+      </c>
+      <c r="H19" t="n">
+        <v>10.409</v>
+      </c>
+      <c r="I19" t="n">
+        <v>12.262</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.08148631029986962</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>OSRM road routing (table service, driving profile): distance and travel time both from the same OSRM response</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>OSRM public routing API (table service)</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>https://router.project-osrm.org/table/v1/driving/</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>2026-09-14T07:07:34.074498+00:00</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Destination is approximately 10.41 km (12.3 min driving) from Chennai Central Railway Station via OSRM road routing. The accessibility score is calculated using the predefined inverse-travel-time formula (1 / (travel_time_min + 0.01)), then normalized across all 20 destinations.</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.03225480414513515</v>
       </c>
     </row>
     <row r="20">
@@ -2827,14 +3787,64 @@
           <t>Express Avenue</t>
         </is>
       </c>
-      <c r="C20" t="n">
-        <v>287.3</v>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Chennai Central Railway Station</t>
+        </is>
       </c>
       <c r="D20" t="n">
-        <v>0.003480682213713888</v>
+        <v>13.0825901</v>
       </c>
       <c r="E20" t="n">
-        <v>0.08249546916449232</v>
+        <v>80.2763077</v>
+      </c>
+      <c r="F20" t="n">
+        <v>13.0588206</v>
+      </c>
+      <c r="G20" t="n">
+        <v>80.2641028</v>
+      </c>
+      <c r="H20" t="n">
+        <v>3.926</v>
+      </c>
+      <c r="I20" t="n">
+        <v>4.788</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.2084201750729471</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>OSRM road routing (table service, driving profile): distance and travel time both from the same OSRM response</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>OSRM public routing API (table service)</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>https://router.project-osrm.org/table/v1/driving/</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>2026-09-14T07:07:34.074498+00:00</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Destination is approximately 3.93 km (4.8 min driving) from Chennai Central Railway Station via OSRM road routing. The accessibility score is calculated using the predefined inverse-travel-time formula (1 / (travel_time_min + 0.01)), then normalized across all 20 destinations.</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.08249915724658161</v>
       </c>
     </row>
     <row r="21">
@@ -2848,14 +3858,64 @@
           <t>MGM Dizzee World</t>
         </is>
       </c>
-      <c r="C21" t="n">
-        <v>2137.6</v>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Chennai Central Railway Station</t>
+        </is>
       </c>
       <c r="D21" t="n">
-        <v>0.000467814371257485</v>
+        <v>13.0825901</v>
       </c>
       <c r="E21" t="n">
-        <v>0.01108764422294098</v>
+        <v>80.2763077</v>
+      </c>
+      <c r="F21" t="n">
+        <v>12.8258571</v>
+      </c>
+      <c r="G21" t="n">
+        <v>80.2452821</v>
+      </c>
+      <c r="H21" t="n">
+        <v>32.884</v>
+      </c>
+      <c r="I21" t="n">
+        <v>35.627</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.02806072340544939</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>OSRM road routing (table service, driving profile): distance and travel time both from the same OSRM response</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>OSRM public routing API (table service)</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>https://router.project-osrm.org/table/v1/driving/</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>2026-09-14T07:07:34.074498+00:00</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Destination is approximately 32.88 km (35.6 min driving) from Chennai Central Railway Station via OSRM road routing. The accessibility score is calculated using the predefined inverse-travel-time formula (1 / (travel_time_min + 0.01)), then normalized across all 20 destinations.</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.01110730298479385</v>
       </c>
     </row>
   </sheetData>
@@ -37956,7 +39016,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>04_HMM_Initial: pi sums to 1</t>
+          <t>04_HMM_Initial: initial_probability sums to 1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
